--- a/hr_employee_data.xlsx
+++ b/hr_employee_data.xlsx
@@ -5,21 +5,38 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\The Moor\Desktop\Project\hr-kpi-excel-dashboard\data\raw\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\The Moor\Desktop\Project\hr-kpi-excel-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="9045"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="9045" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Raw Data" sheetId="1" r:id="rId1"/>
+    <sheet name="Dashboard" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="Slicer_Department">#N/A</definedName>
+  </definedNames>
   <calcPr calcId="152511"/>
+  <pivotCaches>
+    <pivotCache cacheId="3" r:id="rId3"/>
+  </pivotCaches>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
+      <x14:slicerCaches>
+        <x14:slicerCache r:id="rId4"/>
+      </x14:slicerCaches>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
+      <x14:workbookPr/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1657" uniqueCount="527">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1668" uniqueCount="537">
   <si>
     <t>EmployeeID</t>
   </si>
@@ -1600,13 +1617,47 @@
   </si>
   <si>
     <t>TenureYears</t>
+  </si>
+  <si>
+    <t>Total Headcount</t>
+  </si>
+  <si>
+    <t>Attrition Rate</t>
+  </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Sum of AnnualSalary</t>
+  </si>
+  <si>
+    <t>Average Tenure (Years)</t>
+  </si>
+  <si>
+    <t>Female %</t>
+  </si>
+  <si>
+    <t>Male %</t>
+  </si>
+  <si>
+    <t>Rating</t>
+  </si>
+  <si>
+    <t>Count</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="168" formatCode="0.0%"/>
+    <numFmt numFmtId="173" formatCode="0.0"/>
+  </numFmts>
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1624,8 +1675,36 @@
       <sz val="10"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1638,8 +1717,14 @@
         <bgColor rgb="FF305496"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1647,45 +1732,49 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="173" fontId="4" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="4" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="14">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF305496"/>
-          <bgColor rgb="FF305496"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1907,6 +1996,30 @@
         <scheme val="none"/>
       </font>
     </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF305496"/>
+          <bgColor rgb="FF305496"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1920,22 +2033,5975 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[hr_employee_data.xlsx]Dashboard!PivotTable1</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Dashboard!$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Dashboard!$D$2:$D$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Sales</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Dashboard!$E$2:$E$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1901625</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="462644184"/>
+        <c:axId val="462644968"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="462644184"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="462644968"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="462644968"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="462644184"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:cat>
+            <c:strRef>
+              <c:f>Dashboard!$A$6:$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Female %</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Male %</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Dashboard!$B$6:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>0.0%</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0.50641025641025639</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.49358974358974361</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Dashboard!$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Rating</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>Dashboard!$A$10:$A$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Dashboard!$B$9</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Count</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>Dashboard!$B$10:$B$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>77</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>63</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>32</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="463018928"/>
+        <c:axId val="463016968"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="463018928"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="463016968"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="463016968"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="463018928"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>581025</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>235743</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>95251</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>590550</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>171451</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>511969</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>26193</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>226218</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>150018</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>642937</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>145256</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1138237</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>2381</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="5" name="Department"/>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Department"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4643437" y="3657600"/>
+              <a:ext cx="1828800" cy="2524125"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100"/>
+                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
+If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="The Moor" refreshedDate="46231.22154027778" createdVersion="5" refreshedVersion="5" minRefreshableVersion="3" recordCount="200">
+  <cacheSource type="worksheet">
+    <worksheetSource name="Table1"/>
+  </cacheSource>
+  <cacheFields count="13">
+    <cacheField name="EmployeeID" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="FirstName" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="LastName" numFmtId="0">
+      <sharedItems count="20">
+        <s v="Hoffmann"/>
+        <s v="Mueller"/>
+        <s v="Wolf"/>
+        <s v="Koch"/>
+        <s v="Wagner"/>
+        <s v="Fischer"/>
+        <s v="Richter"/>
+        <s v="Braun"/>
+        <s v="Meyer"/>
+        <s v="Schwarz"/>
+        <s v="Neumann"/>
+        <s v="Becker"/>
+        <s v="Schneider"/>
+        <s v="Klein"/>
+        <s v="Kruger"/>
+        <s v="Zimmermann"/>
+        <s v="Schmidt"/>
+        <s v="Weber"/>
+        <s v="Schaefer"/>
+        <s v="Bauer"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Department" numFmtId="0">
+      <sharedItems count="7">
+        <s v="Marketing"/>
+        <s v="Sales"/>
+        <s v="Finance"/>
+        <s v="Customer Support"/>
+        <s v="Human Resources"/>
+        <s v="Engineering"/>
+        <s v="Operations"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="JobTitle" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Gender" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Age" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="22" maxValue="60"/>
+    </cacheField>
+    <cacheField name="HireDate" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="TerminationDate" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="EmploymentStatus" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="AnnualSalary" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="33096" maxValue="98355"/>
+    </cacheField>
+    <cacheField name="PerformanceRating" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="5"/>
+    </cacheField>
+    <cacheField name="TenureYears" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.59452054794520548" maxValue="10.547945205479452"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition pivotCacheId="1"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="200">
+  <r>
+    <s v="E1001"/>
+    <s v="Anna"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Marketing Specialist"/>
+    <s v="Female"/>
+    <n v="30"/>
+    <s v="2024-04-04"/>
+    <m/>
+    <s v="Active"/>
+    <n v="50935"/>
+    <n v="2"/>
+    <n v="2.3150684931506849"/>
+  </r>
+  <r>
+    <s v="E1002"/>
+    <s v="Max"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="Sales Rep"/>
+    <s v="Male"/>
+    <n v="36"/>
+    <s v="2021-08-31"/>
+    <s v="2021-11-23"/>
+    <s v="Terminated"/>
+    <n v="48195"/>
+    <n v="3"/>
+    <n v="4.9095890410958907"/>
+  </r>
+  <r>
+    <s v="E1003"/>
+    <s v="David"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Accountant"/>
+    <s v="Male"/>
+    <n v="22"/>
+    <s v="2024-07-05"/>
+    <m/>
+    <s v="Active"/>
+    <n v="53924"/>
+    <n v="3"/>
+    <n v="2.0630136986301371"/>
+  </r>
+  <r>
+    <s v="E1004"/>
+    <s v="Sophie"/>
+    <x v="3"/>
+    <x v="1"/>
+    <s v="Sales Rep"/>
+    <s v="Female"/>
+    <n v="46"/>
+    <s v="2017-01-31"/>
+    <m/>
+    <s v="Active"/>
+    <n v="44635"/>
+    <n v="4"/>
+    <n v="9.493150684931507"/>
+  </r>
+  <r>
+    <s v="E1005"/>
+    <s v="Lisa"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Financial Analyst"/>
+    <s v="Female"/>
+    <n v="46"/>
+    <s v="2016-11-18"/>
+    <s v="2020-04-01"/>
+    <s v="Terminated"/>
+    <n v="65299"/>
+    <n v="4"/>
+    <n v="9.6958904109589046"/>
+  </r>
+  <r>
+    <s v="E1006"/>
+    <s v="Tom"/>
+    <x v="4"/>
+    <x v="3"/>
+    <s v="Support Agent"/>
+    <s v="Male"/>
+    <n v="24"/>
+    <s v="2023-06-01"/>
+    <m/>
+    <s v="Active"/>
+    <n v="37741"/>
+    <n v="5"/>
+    <n v="3.1589041095890411"/>
+  </r>
+  <r>
+    <s v="E1007"/>
+    <s v="Sofia"/>
+    <x v="5"/>
+    <x v="4"/>
+    <s v="Recruiter"/>
+    <s v="Female"/>
+    <n v="51"/>
+    <s v="2023-02-16"/>
+    <m/>
+    <s v="Active"/>
+    <n v="47664"/>
+    <n v="3"/>
+    <n v="3.4465753424657533"/>
+  </r>
+  <r>
+    <s v="E1008"/>
+    <s v="Hannah"/>
+    <x v="0"/>
+    <x v="3"/>
+    <s v="Support Agent"/>
+    <s v="Female"/>
+    <n v="60"/>
+    <s v="2023-02-13"/>
+    <m/>
+    <s v="Active"/>
+    <n v="41751"/>
+    <n v="4"/>
+    <n v="3.4547945205479453"/>
+  </r>
+  <r>
+    <s v="E1009"/>
+    <s v="Emma"/>
+    <x v="6"/>
+    <x v="5"/>
+    <s v="Engineering Manager"/>
+    <s v="Female"/>
+    <n v="57"/>
+    <s v="2018-06-18"/>
+    <m/>
+    <s v="Active"/>
+    <n v="89916"/>
+    <n v="3"/>
+    <n v="8.1150684931506856"/>
+  </r>
+  <r>
+    <s v="E1010"/>
+    <s v="Mia"/>
+    <x v="3"/>
+    <x v="4"/>
+    <s v="Recruiter"/>
+    <s v="Female"/>
+    <n v="26"/>
+    <s v="2018-05-14"/>
+    <s v="2026-07-01"/>
+    <s v="Terminated"/>
+    <n v="50155"/>
+    <n v="3"/>
+    <n v="8.2109589041095887"/>
+  </r>
+  <r>
+    <s v="E1011"/>
+    <s v="Tim"/>
+    <x v="2"/>
+    <x v="0"/>
+    <s v="Content Strategist"/>
+    <s v="Male"/>
+    <n v="30"/>
+    <s v="2018-10-07"/>
+    <s v="2024-11-21"/>
+    <s v="Terminated"/>
+    <n v="48304"/>
+    <n v="4"/>
+    <n v="7.8109589041095893"/>
+  </r>
+  <r>
+    <s v="E1012"/>
+    <s v="Finn"/>
+    <x v="7"/>
+    <x v="4"/>
+    <s v="Recruiter"/>
+    <s v="Male"/>
+    <n v="36"/>
+    <s v="2017-07-20"/>
+    <s v="2023-03-02"/>
+    <s v="Terminated"/>
+    <n v="46489"/>
+    <n v="4"/>
+    <n v="9.0273972602739718"/>
+  </r>
+  <r>
+    <s v="E1013"/>
+    <s v="Laura"/>
+    <x v="8"/>
+    <x v="6"/>
+    <s v="Operations Manager"/>
+    <s v="Female"/>
+    <n v="60"/>
+    <s v="2016-09-17"/>
+    <m/>
+    <s v="Active"/>
+    <n v="77252"/>
+    <n v="4"/>
+    <n v="9.8657534246575338"/>
+  </r>
+  <r>
+    <s v="E1014"/>
+    <s v="Jan"/>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="Financial Analyst"/>
+    <s v="Male"/>
+    <n v="29"/>
+    <s v="2023-08-24"/>
+    <s v="2025-03-22"/>
+    <s v="Terminated"/>
+    <n v="65501"/>
+    <n v="3"/>
+    <n v="2.9287671232876713"/>
+  </r>
+  <r>
+    <s v="E1015"/>
+    <s v="Tim"/>
+    <x v="8"/>
+    <x v="4"/>
+    <s v="HR Coordinator"/>
+    <s v="Male"/>
+    <n v="38"/>
+    <s v="2021-08-12"/>
+    <m/>
+    <s v="Active"/>
+    <n v="45317"/>
+    <n v="5"/>
+    <n v="4.9616438356164387"/>
+  </r>
+  <r>
+    <s v="E1016"/>
+    <s v="Simon"/>
+    <x v="9"/>
+    <x v="2"/>
+    <s v="Financial Analyst"/>
+    <s v="Male"/>
+    <n v="31"/>
+    <s v="2020-03-11"/>
+    <m/>
+    <s v="Active"/>
+    <n v="63837"/>
+    <n v="5"/>
+    <n v="6.3835616438356162"/>
+  </r>
+  <r>
+    <s v="E1017"/>
+    <s v="Clara"/>
+    <x v="3"/>
+    <x v="4"/>
+    <s v="HR Coordinator"/>
+    <s v="Female"/>
+    <n v="29"/>
+    <s v="2020-01-26"/>
+    <m/>
+    <s v="Active"/>
+    <n v="40923"/>
+    <n v="2"/>
+    <n v="6.506849315068493"/>
+  </r>
+  <r>
+    <s v="E1018"/>
+    <s v="Maria"/>
+    <x v="10"/>
+    <x v="6"/>
+    <s v="Operations Analyst"/>
+    <s v="Female"/>
+    <n v="56"/>
+    <s v="2024-08-02"/>
+    <m/>
+    <s v="Active"/>
+    <n v="49103"/>
+    <n v="4"/>
+    <n v="1.9863013698630136"/>
+  </r>
+  <r>
+    <s v="E1019"/>
+    <s v="Nina"/>
+    <x v="9"/>
+    <x v="6"/>
+    <s v="Operations Manager"/>
+    <s v="Female"/>
+    <n v="35"/>
+    <s v="2022-01-17"/>
+    <m/>
+    <s v="Active"/>
+    <n v="76107"/>
+    <n v="3"/>
+    <n v="4.5287671232876709"/>
+  </r>
+  <r>
+    <s v="E1020"/>
+    <s v="Leon"/>
+    <x v="9"/>
+    <x v="4"/>
+    <s v="HR Coordinator"/>
+    <s v="Male"/>
+    <n v="37"/>
+    <s v="2018-07-09"/>
+    <m/>
+    <s v="Active"/>
+    <n v="42539"/>
+    <n v="1"/>
+    <n v="8.0575342465753419"/>
+  </r>
+  <r>
+    <s v="E1021"/>
+    <s v="Clara"/>
+    <x v="11"/>
+    <x v="1"/>
+    <s v="Sales Rep"/>
+    <s v="Female"/>
+    <n v="25"/>
+    <s v="2018-07-26"/>
+    <m/>
+    <s v="Active"/>
+    <n v="39514"/>
+    <n v="5"/>
+    <n v="8.0109589041095894"/>
+  </r>
+  <r>
+    <s v="E1022"/>
+    <s v="Lea"/>
+    <x v="11"/>
+    <x v="5"/>
+    <s v="Engineering Manager"/>
+    <s v="Female"/>
+    <n v="53"/>
+    <s v="2018-05-27"/>
+    <s v="2019-12-19"/>
+    <s v="Terminated"/>
+    <n v="98355"/>
+    <n v="4"/>
+    <n v="8.1753424657534239"/>
+  </r>
+  <r>
+    <s v="E1023"/>
+    <s v="Mia"/>
+    <x v="10"/>
+    <x v="6"/>
+    <s v="Operations Manager"/>
+    <s v="Female"/>
+    <n v="34"/>
+    <s v="2017-01-21"/>
+    <m/>
+    <s v="Active"/>
+    <n v="81796"/>
+    <n v="3"/>
+    <n v="9.5205479452054789"/>
+  </r>
+  <r>
+    <s v="E1024"/>
+    <s v="Tim"/>
+    <x v="2"/>
+    <x v="6"/>
+    <s v="Operations Analyst"/>
+    <s v="Male"/>
+    <n v="28"/>
+    <s v="2016-09-05"/>
+    <m/>
+    <s v="Active"/>
+    <n v="52559"/>
+    <n v="4"/>
+    <n v="9.8986301369863021"/>
+  </r>
+  <r>
+    <s v="E1025"/>
+    <s v="Sophie"/>
+    <x v="4"/>
+    <x v="0"/>
+    <s v="Marketing Manager"/>
+    <s v="Female"/>
+    <n v="50"/>
+    <s v="2017-07-28"/>
+    <m/>
+    <s v="Active"/>
+    <n v="75006"/>
+    <n v="3"/>
+    <n v="9.0054794520547947"/>
+  </r>
+  <r>
+    <s v="E1026"/>
+    <s v="Sofia"/>
+    <x v="12"/>
+    <x v="4"/>
+    <s v="HR Manager"/>
+    <s v="Female"/>
+    <n v="28"/>
+    <s v="2016-07-26"/>
+    <s v="2026-01-09"/>
+    <s v="Terminated"/>
+    <n v="67241"/>
+    <n v="5"/>
+    <n v="10.010958904109589"/>
+  </r>
+  <r>
+    <s v="E1027"/>
+    <s v="Laura"/>
+    <x v="13"/>
+    <x v="4"/>
+    <s v="Recruiter"/>
+    <s v="Female"/>
+    <n v="35"/>
+    <s v="2025-09-11"/>
+    <m/>
+    <s v="Active"/>
+    <n v="45960"/>
+    <n v="3"/>
+    <n v="0.87671232876712324"/>
+  </r>
+  <r>
+    <s v="E1028"/>
+    <s v="Sarah"/>
+    <x v="0"/>
+    <x v="6"/>
+    <s v="Operations Manager"/>
+    <s v="Female"/>
+    <n v="40"/>
+    <s v="2020-09-28"/>
+    <s v="2026-04-13"/>
+    <s v="Terminated"/>
+    <n v="73536"/>
+    <n v="3"/>
+    <n v="5.8328767123287673"/>
+  </r>
+  <r>
+    <s v="E1029"/>
+    <s v="Anna"/>
+    <x v="7"/>
+    <x v="3"/>
+    <s v="Support Agent"/>
+    <s v="Female"/>
+    <n v="42"/>
+    <s v="2016-08-22"/>
+    <m/>
+    <s v="Active"/>
+    <n v="42571"/>
+    <n v="3"/>
+    <n v="9.9369863013698634"/>
+  </r>
+  <r>
+    <s v="E1030"/>
+    <s v="Anna"/>
+    <x v="9"/>
+    <x v="1"/>
+    <s v="Sales Rep"/>
+    <s v="Female"/>
+    <n v="26"/>
+    <s v="2022-09-03"/>
+    <m/>
+    <s v="Active"/>
+    <n v="42853"/>
+    <n v="3"/>
+    <n v="3.9013698630136986"/>
+  </r>
+  <r>
+    <s v="E1031"/>
+    <s v="Clara"/>
+    <x v="14"/>
+    <x v="1"/>
+    <s v="Sales Manager"/>
+    <s v="Female"/>
+    <n v="27"/>
+    <s v="2020-09-13"/>
+    <s v="2024-04-30"/>
+    <s v="Terminated"/>
+    <n v="79272"/>
+    <n v="3"/>
+    <n v="5.8739726027397259"/>
+  </r>
+  <r>
+    <s v="E1032"/>
+    <s v="David"/>
+    <x v="0"/>
+    <x v="4"/>
+    <s v="HR Coordinator"/>
+    <s v="Male"/>
+    <n v="41"/>
+    <s v="2021-02-15"/>
+    <m/>
+    <s v="Active"/>
+    <n v="38188"/>
+    <n v="1"/>
+    <n v="5.4493150684931511"/>
+  </r>
+  <r>
+    <s v="E1033"/>
+    <s v="Maria"/>
+    <x v="15"/>
+    <x v="0"/>
+    <s v="Marketing Manager"/>
+    <s v="Female"/>
+    <n v="38"/>
+    <s v="2017-06-26"/>
+    <m/>
+    <s v="Active"/>
+    <n v="73127"/>
+    <n v="5"/>
+    <n v="9.0931506849315067"/>
+  </r>
+  <r>
+    <s v="E1034"/>
+    <s v="Jonas"/>
+    <x v="8"/>
+    <x v="4"/>
+    <s v="HR Manager"/>
+    <s v="Male"/>
+    <n v="41"/>
+    <s v="2022-11-10"/>
+    <s v="2022-12-26"/>
+    <s v="Terminated"/>
+    <n v="77942"/>
+    <n v="4"/>
+    <n v="3.7150684931506848"/>
+  </r>
+  <r>
+    <s v="E1035"/>
+    <s v="Finn"/>
+    <x v="5"/>
+    <x v="0"/>
+    <s v="Content Strategist"/>
+    <s v="Male"/>
+    <n v="29"/>
+    <s v="2025-12-23"/>
+    <m/>
+    <s v="Active"/>
+    <n v="53064"/>
+    <n v="3"/>
+    <n v="0.59452054794520548"/>
+  </r>
+  <r>
+    <s v="E1036"/>
+    <s v="Tom"/>
+    <x v="4"/>
+    <x v="3"/>
+    <s v="Support Team Lead"/>
+    <s v="Male"/>
+    <n v="35"/>
+    <s v="2023-09-16"/>
+    <m/>
+    <s v="Active"/>
+    <n v="51280"/>
+    <n v="3"/>
+    <n v="2.8657534246575342"/>
+  </r>
+  <r>
+    <s v="E1037"/>
+    <s v="Maria"/>
+    <x v="13"/>
+    <x v="6"/>
+    <s v="Operations Manager"/>
+    <s v="Female"/>
+    <n v="24"/>
+    <s v="2016-01-15"/>
+    <m/>
+    <s v="Active"/>
+    <n v="73143"/>
+    <n v="4"/>
+    <n v="10.53972602739726"/>
+  </r>
+  <r>
+    <s v="E1038"/>
+    <s v="Lukas"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Finance Manager"/>
+    <s v="Male"/>
+    <n v="49"/>
+    <s v="2022-04-16"/>
+    <m/>
+    <s v="Active"/>
+    <n v="78832"/>
+    <n v="2"/>
+    <n v="4.2849315068493148"/>
+  </r>
+  <r>
+    <s v="E1039"/>
+    <s v="Lea"/>
+    <x v="16"/>
+    <x v="6"/>
+    <s v="Operations Manager"/>
+    <s v="Female"/>
+    <n v="59"/>
+    <s v="2022-03-13"/>
+    <m/>
+    <s v="Active"/>
+    <n v="78041"/>
+    <n v="2"/>
+    <n v="4.3780821917808215"/>
+  </r>
+  <r>
+    <s v="E1040"/>
+    <s v="Felix"/>
+    <x v="16"/>
+    <x v="5"/>
+    <s v="Software Engineer"/>
+    <s v="Male"/>
+    <n v="37"/>
+    <s v="2023-06-24"/>
+    <m/>
+    <s v="Active"/>
+    <n v="67794"/>
+    <n v="4"/>
+    <n v="3.095890410958904"/>
+  </r>
+  <r>
+    <s v="E1041"/>
+    <s v="Tom"/>
+    <x v="17"/>
+    <x v="0"/>
+    <s v="Marketing Specialist"/>
+    <s v="Male"/>
+    <n v="33"/>
+    <s v="2025-11-19"/>
+    <m/>
+    <s v="Active"/>
+    <n v="42406"/>
+    <n v="3"/>
+    <n v="0.68767123287671228"/>
+  </r>
+  <r>
+    <s v="E1042"/>
+    <s v="Erik"/>
+    <x v="13"/>
+    <x v="6"/>
+    <s v="Operations Analyst"/>
+    <s v="Male"/>
+    <n v="39"/>
+    <s v="2017-10-14"/>
+    <m/>
+    <s v="Active"/>
+    <n v="53267"/>
+    <n v="5"/>
+    <n v="8.7917808219178077"/>
+  </r>
+  <r>
+    <s v="E1043"/>
+    <s v="David"/>
+    <x v="4"/>
+    <x v="6"/>
+    <s v="Operations Manager"/>
+    <s v="Male"/>
+    <n v="44"/>
+    <s v="2019-06-04"/>
+    <m/>
+    <s v="Active"/>
+    <n v="74652"/>
+    <n v="1"/>
+    <n v="7.1534246575342468"/>
+  </r>
+  <r>
+    <s v="E1044"/>
+    <s v="Sarah"/>
+    <x v="3"/>
+    <x v="5"/>
+    <s v="Software Engineer"/>
+    <s v="Female"/>
+    <n v="39"/>
+    <s v="2019-12-09"/>
+    <s v="2024-07-02"/>
+    <s v="Terminated"/>
+    <n v="70785"/>
+    <n v="3"/>
+    <n v="6.6383561643835618"/>
+  </r>
+  <r>
+    <s v="E1045"/>
+    <s v="Maria"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Marketing Manager"/>
+    <s v="Female"/>
+    <n v="38"/>
+    <s v="2016-06-05"/>
+    <m/>
+    <s v="Active"/>
+    <n v="81774"/>
+    <n v="3"/>
+    <n v="10.150684931506849"/>
+  </r>
+  <r>
+    <s v="E1046"/>
+    <s v="Tim"/>
+    <x v="14"/>
+    <x v="2"/>
+    <s v="Financial Analyst"/>
+    <s v="Male"/>
+    <n v="46"/>
+    <s v="2022-06-19"/>
+    <m/>
+    <s v="Active"/>
+    <n v="59173"/>
+    <n v="2"/>
+    <n v="4.1095890410958908"/>
+  </r>
+  <r>
+    <s v="E1047"/>
+    <s v="Max"/>
+    <x v="9"/>
+    <x v="6"/>
+    <s v="Operations Analyst"/>
+    <s v="Male"/>
+    <n v="45"/>
+    <s v="2020-11-01"/>
+    <m/>
+    <s v="Active"/>
+    <n v="57882"/>
+    <n v="5"/>
+    <n v="5.7397260273972606"/>
+  </r>
+  <r>
+    <s v="E1048"/>
+    <s v="Noah"/>
+    <x v="5"/>
+    <x v="3"/>
+    <s v="Support Team Lead"/>
+    <s v="Male"/>
+    <n v="54"/>
+    <s v="2019-06-20"/>
+    <m/>
+    <s v="Active"/>
+    <n v="48344"/>
+    <n v="3"/>
+    <n v="7.1095890410958908"/>
+  </r>
+  <r>
+    <s v="E1049"/>
+    <s v="Jan"/>
+    <x v="17"/>
+    <x v="0"/>
+    <s v="Content Strategist"/>
+    <s v="Male"/>
+    <n v="46"/>
+    <s v="2023-08-06"/>
+    <m/>
+    <s v="Active"/>
+    <n v="54084"/>
+    <n v="4"/>
+    <n v="2.978082191780822"/>
+  </r>
+  <r>
+    <s v="E1050"/>
+    <s v="Jan"/>
+    <x v="1"/>
+    <x v="5"/>
+    <s v="QA Engineer"/>
+    <s v="Male"/>
+    <n v="35"/>
+    <s v="2020-10-26"/>
+    <s v="2024-07-06"/>
+    <s v="Terminated"/>
+    <n v="56618"/>
+    <n v="3"/>
+    <n v="5.7561643835616438"/>
+  </r>
+  <r>
+    <s v="E1051"/>
+    <s v="Lea"/>
+    <x v="10"/>
+    <x v="6"/>
+    <s v="Operations Analyst"/>
+    <s v="Female"/>
+    <n v="27"/>
+    <s v="2019-03-08"/>
+    <s v="2026-05-12"/>
+    <s v="Terminated"/>
+    <n v="57145"/>
+    <n v="3"/>
+    <n v="7.3945205479452056"/>
+  </r>
+  <r>
+    <s v="E1052"/>
+    <s v="Hannah"/>
+    <x v="18"/>
+    <x v="0"/>
+    <s v="Marketing Specialist"/>
+    <s v="Female"/>
+    <n v="31"/>
+    <s v="2016-04-10"/>
+    <m/>
+    <s v="Active"/>
+    <n v="46011"/>
+    <n v="5"/>
+    <n v="10.304109589041095"/>
+  </r>
+  <r>
+    <s v="E1053"/>
+    <s v="Emma"/>
+    <x v="13"/>
+    <x v="3"/>
+    <s v="Support Agent"/>
+    <s v="Female"/>
+    <n v="46"/>
+    <s v="2021-07-17"/>
+    <m/>
+    <s v="Active"/>
+    <n v="36997"/>
+    <n v="3"/>
+    <n v="5.0328767123287674"/>
+  </r>
+  <r>
+    <s v="E1054"/>
+    <s v="Elena"/>
+    <x v="5"/>
+    <x v="6"/>
+    <s v="Operations Manager"/>
+    <s v="Female"/>
+    <n v="36"/>
+    <s v="2017-12-21"/>
+    <s v="2023-04-06"/>
+    <s v="Terminated"/>
+    <n v="71822"/>
+    <n v="4"/>
+    <n v="8.6054794520547944"/>
+  </r>
+  <r>
+    <s v="E1055"/>
+    <s v="Emma"/>
+    <x v="17"/>
+    <x v="6"/>
+    <s v="Operations Manager"/>
+    <s v="Female"/>
+    <n v="55"/>
+    <s v="2022-04-08"/>
+    <s v="2024-02-16"/>
+    <s v="Terminated"/>
+    <n v="78251"/>
+    <n v="4"/>
+    <n v="4.3068493150684928"/>
+  </r>
+  <r>
+    <s v="E1056"/>
+    <s v="Simon"/>
+    <x v="15"/>
+    <x v="4"/>
+    <s v="HR Coordinator"/>
+    <s v="Male"/>
+    <n v="52"/>
+    <s v="2021-01-17"/>
+    <m/>
+    <s v="Active"/>
+    <n v="41050"/>
+    <n v="4"/>
+    <n v="5.5287671232876709"/>
+  </r>
+  <r>
+    <s v="E1057"/>
+    <s v="Erik"/>
+    <x v="9"/>
+    <x v="4"/>
+    <s v="HR Manager"/>
+    <s v="Male"/>
+    <n v="37"/>
+    <s v="2019-01-29"/>
+    <m/>
+    <s v="Active"/>
+    <n v="68269"/>
+    <n v="4"/>
+    <n v="7.4986301369863018"/>
+  </r>
+  <r>
+    <s v="E1058"/>
+    <s v="Nina"/>
+    <x v="3"/>
+    <x v="5"/>
+    <s v="Engineering Manager"/>
+    <s v="Female"/>
+    <n v="27"/>
+    <s v="2017-07-20"/>
+    <m/>
+    <s v="Active"/>
+    <n v="92788"/>
+    <n v="3"/>
+    <n v="9.0273972602739718"/>
+  </r>
+  <r>
+    <s v="E1059"/>
+    <s v="Lisa"/>
+    <x v="4"/>
+    <x v="1"/>
+    <s v="Account Executive"/>
+    <s v="Female"/>
+    <n v="48"/>
+    <s v="2019-09-17"/>
+    <s v="2025-01-06"/>
+    <s v="Terminated"/>
+    <n v="58812"/>
+    <n v="2"/>
+    <n v="6.8657534246575347"/>
+  </r>
+  <r>
+    <s v="E1060"/>
+    <s v="Tim"/>
+    <x v="7"/>
+    <x v="3"/>
+    <s v="Support Agent"/>
+    <s v="Male"/>
+    <n v="58"/>
+    <s v="2020-04-07"/>
+    <m/>
+    <s v="Active"/>
+    <n v="33096"/>
+    <n v="5"/>
+    <n v="6.3095890410958901"/>
+  </r>
+  <r>
+    <s v="E1061"/>
+    <s v="Erik"/>
+    <x v="6"/>
+    <x v="6"/>
+    <s v="Operations Manager"/>
+    <s v="Male"/>
+    <n v="56"/>
+    <s v="2024-05-19"/>
+    <s v="2026-02-25"/>
+    <s v="Terminated"/>
+    <n v="74613"/>
+    <n v="3"/>
+    <n v="2.1917808219178081"/>
+  </r>
+  <r>
+    <s v="E1062"/>
+    <s v="Tim"/>
+    <x v="10"/>
+    <x v="1"/>
+    <s v="Account Executive"/>
+    <s v="Male"/>
+    <n v="43"/>
+    <s v="2023-07-02"/>
+    <m/>
+    <s v="Active"/>
+    <n v="54704"/>
+    <n v="4"/>
+    <n v="3.0739726027397261"/>
+  </r>
+  <r>
+    <s v="E1063"/>
+    <s v="Clara"/>
+    <x v="15"/>
+    <x v="1"/>
+    <s v="Account Executive"/>
+    <s v="Female"/>
+    <n v="59"/>
+    <s v="2022-04-30"/>
+    <m/>
+    <s v="Active"/>
+    <n v="53375"/>
+    <n v="4"/>
+    <n v="4.2465753424657535"/>
+  </r>
+  <r>
+    <s v="E1064"/>
+    <s v="Sofia"/>
+    <x v="2"/>
+    <x v="0"/>
+    <s v="Marketing Specialist"/>
+    <s v="Female"/>
+    <n v="38"/>
+    <s v="2020-04-01"/>
+    <m/>
+    <s v="Active"/>
+    <n v="45467"/>
+    <n v="3"/>
+    <n v="6.3260273972602743"/>
+  </r>
+  <r>
+    <s v="E1065"/>
+    <s v="Erik"/>
+    <x v="6"/>
+    <x v="5"/>
+    <s v="QA Engineer"/>
+    <s v="Male"/>
+    <n v="38"/>
+    <s v="2025-05-12"/>
+    <m/>
+    <s v="Active"/>
+    <n v="56705"/>
+    <n v="1"/>
+    <n v="1.210958904109589"/>
+  </r>
+  <r>
+    <s v="E1066"/>
+    <s v="Julia"/>
+    <x v="11"/>
+    <x v="3"/>
+    <s v="Support Agent"/>
+    <s v="Female"/>
+    <n v="24"/>
+    <s v="2024-06-16"/>
+    <m/>
+    <s v="Active"/>
+    <n v="37051"/>
+    <n v="3"/>
+    <n v="2.1150684931506851"/>
+  </r>
+  <r>
+    <s v="E1067"/>
+    <s v="Clara"/>
+    <x v="17"/>
+    <x v="0"/>
+    <s v="Marketing Specialist"/>
+    <s v="Female"/>
+    <n v="52"/>
+    <s v="2023-07-05"/>
+    <m/>
+    <s v="Active"/>
+    <n v="51240"/>
+    <n v="5"/>
+    <n v="3.0657534246575344"/>
+  </r>
+  <r>
+    <s v="E1068"/>
+    <s v="Ben"/>
+    <x v="0"/>
+    <x v="6"/>
+    <s v="Operations Manager"/>
+    <s v="Male"/>
+    <n v="32"/>
+    <s v="2022-10-17"/>
+    <s v="2023-07-08"/>
+    <s v="Terminated"/>
+    <n v="73683"/>
+    <n v="5"/>
+    <n v="3.7808219178082192"/>
+  </r>
+  <r>
+    <s v="E1069"/>
+    <s v="Clara"/>
+    <x v="1"/>
+    <x v="5"/>
+    <s v="Engineering Manager"/>
+    <s v="Female"/>
+    <n v="46"/>
+    <s v="2020-06-12"/>
+    <m/>
+    <s v="Active"/>
+    <n v="90245"/>
+    <n v="4"/>
+    <n v="6.1287671232876715"/>
+  </r>
+  <r>
+    <s v="E1070"/>
+    <s v="Maria"/>
+    <x v="18"/>
+    <x v="6"/>
+    <s v="Operations Analyst"/>
+    <s v="Female"/>
+    <n v="58"/>
+    <s v="2024-10-10"/>
+    <m/>
+    <s v="Active"/>
+    <n v="52688"/>
+    <n v="4"/>
+    <n v="1.7972602739726027"/>
+  </r>
+  <r>
+    <s v="E1071"/>
+    <s v="Paul"/>
+    <x v="9"/>
+    <x v="3"/>
+    <s v="Support Team Lead"/>
+    <s v="Male"/>
+    <n v="22"/>
+    <s v="2025-07-11"/>
+    <m/>
+    <s v="Active"/>
+    <n v="51031"/>
+    <n v="2"/>
+    <n v="1.0465753424657533"/>
+  </r>
+  <r>
+    <s v="E1072"/>
+    <s v="Noah"/>
+    <x v="2"/>
+    <x v="3"/>
+    <s v="Support Agent"/>
+    <s v="Male"/>
+    <n v="49"/>
+    <s v="2017-12-22"/>
+    <s v="2025-05-08"/>
+    <s v="Terminated"/>
+    <n v="37425"/>
+    <n v="4"/>
+    <n v="8.6027397260273979"/>
+  </r>
+  <r>
+    <s v="E1073"/>
+    <s v="Leon"/>
+    <x v="13"/>
+    <x v="6"/>
+    <s v="Operations Manager"/>
+    <s v="Male"/>
+    <n v="42"/>
+    <s v="2025-07-20"/>
+    <m/>
+    <s v="Active"/>
+    <n v="72419"/>
+    <n v="3"/>
+    <n v="1.021917808219178"/>
+  </r>
+  <r>
+    <s v="E1074"/>
+    <s v="David"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Finance Manager"/>
+    <s v="Male"/>
+    <n v="46"/>
+    <s v="2019-10-09"/>
+    <m/>
+    <s v="Active"/>
+    <n v="85098"/>
+    <n v="5"/>
+    <n v="6.8054794520547945"/>
+  </r>
+  <r>
+    <s v="E1075"/>
+    <s v="Emma"/>
+    <x v="4"/>
+    <x v="5"/>
+    <s v="QA Engineer"/>
+    <s v="Female"/>
+    <n v="43"/>
+    <s v="2019-02-19"/>
+    <s v="2022-04-25"/>
+    <s v="Terminated"/>
+    <n v="58106"/>
+    <n v="1"/>
+    <n v="7.441095890410959"/>
+  </r>
+  <r>
+    <s v="E1076"/>
+    <s v="Maria"/>
+    <x v="11"/>
+    <x v="3"/>
+    <s v="Support Team Lead"/>
+    <s v="Female"/>
+    <n v="53"/>
+    <s v="2022-03-24"/>
+    <m/>
+    <s v="Active"/>
+    <n v="50800"/>
+    <n v="4"/>
+    <n v="4.3479452054794523"/>
+  </r>
+  <r>
+    <s v="E1077"/>
+    <s v="Leon"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="Account Executive"/>
+    <s v="Male"/>
+    <n v="36"/>
+    <s v="2020-07-14"/>
+    <m/>
+    <s v="Active"/>
+    <n v="57016"/>
+    <n v="4"/>
+    <n v="6.0410958904109586"/>
+  </r>
+  <r>
+    <s v="E1078"/>
+    <s v="Leon"/>
+    <x v="15"/>
+    <x v="2"/>
+    <s v="Accountant"/>
+    <s v="Male"/>
+    <n v="49"/>
+    <s v="2024-05-13"/>
+    <s v="2025-05-16"/>
+    <s v="Terminated"/>
+    <n v="52764"/>
+    <n v="4"/>
+    <n v="2.2082191780821918"/>
+  </r>
+  <r>
+    <s v="E1079"/>
+    <s v="Jonas"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Marketing Specialist"/>
+    <s v="Male"/>
+    <n v="34"/>
+    <s v="2019-07-16"/>
+    <m/>
+    <s v="Active"/>
+    <n v="50779"/>
+    <n v="5"/>
+    <n v="7.0383561643835613"/>
+  </r>
+  <r>
+    <s v="E1080"/>
+    <s v="Sophie"/>
+    <x v="4"/>
+    <x v="3"/>
+    <s v="Support Team Lead"/>
+    <s v="Female"/>
+    <n v="39"/>
+    <s v="2024-02-15"/>
+    <s v="2026-05-03"/>
+    <s v="Terminated"/>
+    <n v="51595"/>
+    <n v="4"/>
+    <n v="2.4493150684931506"/>
+  </r>
+  <r>
+    <s v="E1081"/>
+    <s v="Sofia"/>
+    <x v="4"/>
+    <x v="5"/>
+    <s v="Software Engineer"/>
+    <s v="Female"/>
+    <n v="45"/>
+    <s v="2018-01-04"/>
+    <m/>
+    <s v="Active"/>
+    <n v="62231"/>
+    <n v="4"/>
+    <n v="8.5671232876712331"/>
+  </r>
+  <r>
+    <s v="E1082"/>
+    <s v="Nina"/>
+    <x v="16"/>
+    <x v="1"/>
+    <s v="Sales Manager"/>
+    <s v="Female"/>
+    <n v="40"/>
+    <s v="2023-10-27"/>
+    <m/>
+    <s v="Active"/>
+    <n v="85450"/>
+    <n v="5"/>
+    <n v="2.7534246575342465"/>
+  </r>
+  <r>
+    <s v="E1083"/>
+    <s v="Paul"/>
+    <x v="1"/>
+    <x v="2"/>
+    <s v="Accountant"/>
+    <s v="Male"/>
+    <n v="52"/>
+    <s v="2021-05-14"/>
+    <m/>
+    <s v="Active"/>
+    <n v="52582"/>
+    <n v="3"/>
+    <n v="5.2082191780821914"/>
+  </r>
+  <r>
+    <s v="E1084"/>
+    <s v="Nina"/>
+    <x v="10"/>
+    <x v="1"/>
+    <s v="Sales Rep"/>
+    <s v="Female"/>
+    <n v="47"/>
+    <s v="2021-07-07"/>
+    <m/>
+    <s v="Active"/>
+    <n v="48453"/>
+    <n v="4"/>
+    <n v="5.0602739726027401"/>
+  </r>
+  <r>
+    <s v="E1085"/>
+    <s v="Laura"/>
+    <x v="17"/>
+    <x v="6"/>
+    <s v="Operations Manager"/>
+    <s v="Female"/>
+    <n v="27"/>
+    <s v="2018-10-13"/>
+    <m/>
+    <s v="Active"/>
+    <n v="80143"/>
+    <n v="4"/>
+    <n v="7.7945205479452051"/>
+  </r>
+  <r>
+    <s v="E1086"/>
+    <s v="Mia"/>
+    <x v="9"/>
+    <x v="4"/>
+    <s v="Recruiter"/>
+    <s v="Female"/>
+    <n v="50"/>
+    <s v="2019-05-02"/>
+    <s v="2024-03-22"/>
+    <s v="Terminated"/>
+    <n v="50003"/>
+    <n v="4"/>
+    <n v="7.2438356164383562"/>
+  </r>
+  <r>
+    <s v="E1087"/>
+    <s v="Clara"/>
+    <x v="5"/>
+    <x v="6"/>
+    <s v="Operations Analyst"/>
+    <s v="Female"/>
+    <n v="35"/>
+    <s v="2018-12-19"/>
+    <m/>
+    <s v="Active"/>
+    <n v="49573"/>
+    <n v="3"/>
+    <n v="7.6109589041095891"/>
+  </r>
+  <r>
+    <s v="E1088"/>
+    <s v="Laura"/>
+    <x v="1"/>
+    <x v="4"/>
+    <s v="Recruiter"/>
+    <s v="Female"/>
+    <n v="60"/>
+    <s v="2021-04-08"/>
+    <m/>
+    <s v="Active"/>
+    <n v="45534"/>
+    <n v="3"/>
+    <n v="5.3068493150684928"/>
+  </r>
+  <r>
+    <s v="E1089"/>
+    <s v="Ben"/>
+    <x v="2"/>
+    <x v="1"/>
+    <s v="Sales Manager"/>
+    <s v="Male"/>
+    <n v="36"/>
+    <s v="2018-12-19"/>
+    <s v="2026-06-18"/>
+    <s v="Terminated"/>
+    <n v="78241"/>
+    <n v="3"/>
+    <n v="7.6109589041095891"/>
+  </r>
+  <r>
+    <s v="E1090"/>
+    <s v="Hannah"/>
+    <x v="17"/>
+    <x v="5"/>
+    <s v="Software Engineer"/>
+    <s v="Female"/>
+    <n v="26"/>
+    <s v="2016-09-01"/>
+    <m/>
+    <s v="Active"/>
+    <n v="67039"/>
+    <n v="4"/>
+    <n v="9.9095890410958898"/>
+  </r>
+  <r>
+    <s v="E1091"/>
+    <s v="Leon"/>
+    <x v="5"/>
+    <x v="4"/>
+    <s v="HR Manager"/>
+    <s v="Male"/>
+    <n v="41"/>
+    <s v="2023-11-06"/>
+    <m/>
+    <s v="Active"/>
+    <n v="71460"/>
+    <n v="3"/>
+    <n v="2.7260273972602738"/>
+  </r>
+  <r>
+    <s v="E1092"/>
+    <s v="Leon"/>
+    <x v="12"/>
+    <x v="2"/>
+    <s v="Financial Analyst"/>
+    <s v="Male"/>
+    <n v="49"/>
+    <s v="2024-03-27"/>
+    <m/>
+    <s v="Active"/>
+    <n v="64891"/>
+    <n v="3"/>
+    <n v="2.3369863013698629"/>
+  </r>
+  <r>
+    <s v="E1093"/>
+    <s v="Sophie"/>
+    <x v="7"/>
+    <x v="2"/>
+    <s v="Financial Analyst"/>
+    <s v="Female"/>
+    <n v="39"/>
+    <s v="2022-06-18"/>
+    <m/>
+    <s v="Active"/>
+    <n v="57870"/>
+    <n v="3"/>
+    <n v="4.1123287671232873"/>
+  </r>
+  <r>
+    <s v="E1094"/>
+    <s v="Finn"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Marketing Manager"/>
+    <s v="Male"/>
+    <n v="49"/>
+    <s v="2023-02-13"/>
+    <m/>
+    <s v="Active"/>
+    <n v="73494"/>
+    <n v="3"/>
+    <n v="3.4547945205479453"/>
+  </r>
+  <r>
+    <s v="E1095"/>
+    <s v="Felix"/>
+    <x v="3"/>
+    <x v="3"/>
+    <s v="Support Agent"/>
+    <s v="Male"/>
+    <n v="32"/>
+    <s v="2019-09-12"/>
+    <m/>
+    <s v="Active"/>
+    <n v="41117"/>
+    <n v="3"/>
+    <n v="6.8794520547945206"/>
+  </r>
+  <r>
+    <s v="E1096"/>
+    <s v="Simon"/>
+    <x v="15"/>
+    <x v="1"/>
+    <s v="Account Executive"/>
+    <s v="Male"/>
+    <n v="27"/>
+    <s v="2019-07-12"/>
+    <m/>
+    <s v="Active"/>
+    <n v="57296"/>
+    <n v="2"/>
+    <n v="7.0493150684931507"/>
+  </r>
+  <r>
+    <s v="E1097"/>
+    <s v="Simon"/>
+    <x v="9"/>
+    <x v="6"/>
+    <s v="Operations Analyst"/>
+    <s v="Male"/>
+    <n v="56"/>
+    <s v="2021-03-07"/>
+    <m/>
+    <s v="Active"/>
+    <n v="47888"/>
+    <n v="3"/>
+    <n v="5.3945205479452056"/>
+  </r>
+  <r>
+    <s v="E1098"/>
+    <s v="Tom"/>
+    <x v="10"/>
+    <x v="3"/>
+    <s v="Support Team Lead"/>
+    <s v="Male"/>
+    <n v="25"/>
+    <s v="2018-04-13"/>
+    <m/>
+    <s v="Active"/>
+    <n v="51998"/>
+    <n v="3"/>
+    <n v="8.2958904109589042"/>
+  </r>
+  <r>
+    <s v="E1099"/>
+    <s v="Leon"/>
+    <x v="10"/>
+    <x v="1"/>
+    <s v="Sales Rep"/>
+    <s v="Male"/>
+    <n v="60"/>
+    <s v="2024-12-17"/>
+    <m/>
+    <s v="Active"/>
+    <n v="41594"/>
+    <n v="3"/>
+    <n v="1.6109589041095891"/>
+  </r>
+  <r>
+    <s v="E1100"/>
+    <s v="Lea"/>
+    <x v="13"/>
+    <x v="1"/>
+    <s v="Sales Rep"/>
+    <s v="Female"/>
+    <n v="29"/>
+    <s v="2021-03-05"/>
+    <m/>
+    <s v="Active"/>
+    <n v="49612"/>
+    <n v="4"/>
+    <n v="5.4"/>
+  </r>
+  <r>
+    <s v="E1101"/>
+    <s v="Finn"/>
+    <x v="18"/>
+    <x v="2"/>
+    <s v="Finance Manager"/>
+    <s v="Male"/>
+    <n v="39"/>
+    <s v="2020-08-28"/>
+    <m/>
+    <s v="Active"/>
+    <n v="84736"/>
+    <n v="3"/>
+    <n v="5.9178082191780819"/>
+  </r>
+  <r>
+    <s v="E1102"/>
+    <s v="Sarah"/>
+    <x v="4"/>
+    <x v="2"/>
+    <s v="Finance Manager"/>
+    <s v="Female"/>
+    <n v="30"/>
+    <s v="2025-09-09"/>
+    <m/>
+    <s v="Active"/>
+    <n v="81526"/>
+    <n v="4"/>
+    <n v="0.88219178082191785"/>
+  </r>
+  <r>
+    <s v="E1103"/>
+    <s v="Felix"/>
+    <x v="9"/>
+    <x v="5"/>
+    <s v="Software Engineer"/>
+    <s v="Male"/>
+    <n v="40"/>
+    <s v="2024-02-21"/>
+    <m/>
+    <s v="Active"/>
+    <n v="71616"/>
+    <n v="4"/>
+    <n v="2.4328767123287673"/>
+  </r>
+  <r>
+    <s v="E1104"/>
+    <s v="Simon"/>
+    <x v="17"/>
+    <x v="4"/>
+    <s v="HR Manager"/>
+    <s v="Male"/>
+    <n v="52"/>
+    <s v="2019-11-14"/>
+    <m/>
+    <s v="Active"/>
+    <n v="76042"/>
+    <n v="4"/>
+    <n v="6.7068493150684931"/>
+  </r>
+  <r>
+    <s v="E1105"/>
+    <s v="Leon"/>
+    <x v="3"/>
+    <x v="6"/>
+    <s v="Operations Analyst"/>
+    <s v="Male"/>
+    <n v="37"/>
+    <s v="2022-05-31"/>
+    <m/>
+    <s v="Active"/>
+    <n v="50826"/>
+    <n v="5"/>
+    <n v="4.161643835616438"/>
+  </r>
+  <r>
+    <s v="E1106"/>
+    <s v="Max"/>
+    <x v="3"/>
+    <x v="3"/>
+    <s v="Support Team Lead"/>
+    <s v="Male"/>
+    <n v="46"/>
+    <s v="2020-04-30"/>
+    <m/>
+    <s v="Active"/>
+    <n v="51115"/>
+    <n v="5"/>
+    <n v="6.2465753424657535"/>
+  </r>
+  <r>
+    <s v="E1107"/>
+    <s v="Lea"/>
+    <x v="7"/>
+    <x v="5"/>
+    <s v="Software Engineer"/>
+    <s v="Female"/>
+    <n v="50"/>
+    <s v="2017-02-12"/>
+    <s v="2022-04-28"/>
+    <s v="Terminated"/>
+    <n v="62251"/>
+    <n v="4"/>
+    <n v="9.4602739726027405"/>
+  </r>
+  <r>
+    <s v="E1108"/>
+    <s v="Simon"/>
+    <x v="17"/>
+    <x v="1"/>
+    <s v="Account Executive"/>
+    <s v="Male"/>
+    <n v="38"/>
+    <s v="2019-10-18"/>
+    <s v="2024-05-02"/>
+    <s v="Terminated"/>
+    <n v="62646"/>
+    <n v="2"/>
+    <n v="6.7808219178082192"/>
+  </r>
+  <r>
+    <s v="E1109"/>
+    <s v="Simon"/>
+    <x v="15"/>
+    <x v="4"/>
+    <s v="Recruiter"/>
+    <s v="Male"/>
+    <n v="53"/>
+    <s v="2025-10-13"/>
+    <s v="2025-11-30"/>
+    <s v="Terminated"/>
+    <n v="55116"/>
+    <n v="2"/>
+    <n v="0.78904109589041094"/>
+  </r>
+  <r>
+    <s v="E1110"/>
+    <s v="David"/>
+    <x v="12"/>
+    <x v="4"/>
+    <s v="HR Coordinator"/>
+    <s v="Male"/>
+    <n v="28"/>
+    <s v="2020-12-22"/>
+    <m/>
+    <s v="Active"/>
+    <n v="41906"/>
+    <n v="5"/>
+    <n v="5.6"/>
+  </r>
+  <r>
+    <s v="E1111"/>
+    <s v="Julia"/>
+    <x v="16"/>
+    <x v="5"/>
+    <s v="QA Engineer"/>
+    <s v="Female"/>
+    <n v="45"/>
+    <s v="2020-10-30"/>
+    <m/>
+    <s v="Active"/>
+    <n v="53000"/>
+    <n v="4"/>
+    <n v="5.7452054794520544"/>
+  </r>
+  <r>
+    <s v="E1112"/>
+    <s v="Laura"/>
+    <x v="8"/>
+    <x v="1"/>
+    <s v="Sales Manager"/>
+    <s v="Female"/>
+    <n v="46"/>
+    <s v="2022-12-13"/>
+    <m/>
+    <s v="Active"/>
+    <n v="83153"/>
+    <n v="5"/>
+    <n v="3.6246575342465754"/>
+  </r>
+  <r>
+    <s v="E1113"/>
+    <s v="Sophie"/>
+    <x v="2"/>
+    <x v="3"/>
+    <s v="Support Team Lead"/>
+    <s v="Female"/>
+    <n v="51"/>
+    <s v="2018-11-11"/>
+    <m/>
+    <s v="Active"/>
+    <n v="50622"/>
+    <n v="5"/>
+    <n v="7.7150684931506852"/>
+  </r>
+  <r>
+    <s v="E1114"/>
+    <s v="Maria"/>
+    <x v="2"/>
+    <x v="5"/>
+    <s v="Engineering Manager"/>
+    <s v="Female"/>
+    <n v="41"/>
+    <s v="2023-03-02"/>
+    <m/>
+    <s v="Active"/>
+    <n v="93097"/>
+    <n v="3"/>
+    <n v="3.408219178082192"/>
+  </r>
+  <r>
+    <s v="E1115"/>
+    <s v="David"/>
+    <x v="6"/>
+    <x v="6"/>
+    <s v="Operations Manager"/>
+    <s v="Male"/>
+    <n v="28"/>
+    <s v="2018-08-29"/>
+    <m/>
+    <s v="Active"/>
+    <n v="80370"/>
+    <n v="3"/>
+    <n v="7.9178082191780819"/>
+  </r>
+  <r>
+    <s v="E1116"/>
+    <s v="Ben"/>
+    <x v="18"/>
+    <x v="1"/>
+    <s v="Sales Manager"/>
+    <s v="Male"/>
+    <n v="47"/>
+    <s v="2019-01-29"/>
+    <m/>
+    <s v="Active"/>
+    <n v="84272"/>
+    <n v="5"/>
+    <n v="7.4986301369863018"/>
+  </r>
+  <r>
+    <s v="E1117"/>
+    <s v="Elena"/>
+    <x v="14"/>
+    <x v="3"/>
+    <s v="Support Team Lead"/>
+    <s v="Female"/>
+    <n v="40"/>
+    <s v="2024-09-12"/>
+    <m/>
+    <s v="Active"/>
+    <n v="52946"/>
+    <n v="4"/>
+    <n v="1.8739726027397261"/>
+  </r>
+  <r>
+    <s v="E1118"/>
+    <s v="Hannah"/>
+    <x v="4"/>
+    <x v="2"/>
+    <s v="Accountant"/>
+    <s v="Female"/>
+    <n v="30"/>
+    <s v="2023-01-17"/>
+    <m/>
+    <s v="Active"/>
+    <n v="57280"/>
+    <n v="4"/>
+    <n v="3.5287671232876714"/>
+  </r>
+  <r>
+    <s v="E1119"/>
+    <s v="Erik"/>
+    <x v="2"/>
+    <x v="1"/>
+    <s v="Sales Manager"/>
+    <s v="Male"/>
+    <n v="45"/>
+    <s v="2024-03-18"/>
+    <m/>
+    <s v="Active"/>
+    <n v="76476"/>
+    <n v="5"/>
+    <n v="2.3616438356164382"/>
+  </r>
+  <r>
+    <s v="E1120"/>
+    <s v="Ben"/>
+    <x v="13"/>
+    <x v="0"/>
+    <s v="Marketing Specialist"/>
+    <s v="Male"/>
+    <n v="30"/>
+    <s v="2024-10-26"/>
+    <s v="2025-12-04"/>
+    <s v="Terminated"/>
+    <n v="50697"/>
+    <n v="3"/>
+    <n v="1.7534246575342465"/>
+  </r>
+  <r>
+    <s v="E1121"/>
+    <s v="Simon"/>
+    <x v="8"/>
+    <x v="5"/>
+    <s v="QA Engineer"/>
+    <s v="Male"/>
+    <n v="40"/>
+    <s v="2024-05-15"/>
+    <m/>
+    <s v="Active"/>
+    <n v="50886"/>
+    <n v="3"/>
+    <n v="2.2027397260273971"/>
+  </r>
+  <r>
+    <s v="E1122"/>
+    <s v="Laura"/>
+    <x v="11"/>
+    <x v="6"/>
+    <s v="Operations Manager"/>
+    <s v="Female"/>
+    <n v="57"/>
+    <s v="2020-02-07"/>
+    <m/>
+    <s v="Active"/>
+    <n v="77464"/>
+    <n v="1"/>
+    <n v="6.4739726027397264"/>
+  </r>
+  <r>
+    <s v="E1123"/>
+    <s v="Emma"/>
+    <x v="19"/>
+    <x v="3"/>
+    <s v="Support Team Lead"/>
+    <s v="Female"/>
+    <n v="59"/>
+    <s v="2020-04-09"/>
+    <m/>
+    <s v="Active"/>
+    <n v="44775"/>
+    <n v="4"/>
+    <n v="6.3041095890410963"/>
+  </r>
+  <r>
+    <s v="E1124"/>
+    <s v="Max"/>
+    <x v="14"/>
+    <x v="2"/>
+    <s v="Accountant"/>
+    <s v="Male"/>
+    <n v="36"/>
+    <s v="2023-04-06"/>
+    <m/>
+    <s v="Active"/>
+    <n v="57410"/>
+    <n v="4"/>
+    <n v="3.3123287671232875"/>
+  </r>
+  <r>
+    <s v="E1125"/>
+    <s v="Noah"/>
+    <x v="13"/>
+    <x v="1"/>
+    <s v="Sales Rep"/>
+    <s v="Male"/>
+    <n v="24"/>
+    <s v="2016-06-01"/>
+    <m/>
+    <s v="Active"/>
+    <n v="47071"/>
+    <n v="2"/>
+    <n v="10.161643835616438"/>
+  </r>
+  <r>
+    <s v="E1126"/>
+    <s v="Elena"/>
+    <x v="15"/>
+    <x v="0"/>
+    <s v="Content Strategist"/>
+    <s v="Female"/>
+    <n v="51"/>
+    <s v="2020-02-28"/>
+    <s v="2024-12-09"/>
+    <s v="Terminated"/>
+    <n v="53622"/>
+    <n v="4"/>
+    <n v="6.4164383561643836"/>
+  </r>
+  <r>
+    <s v="E1127"/>
+    <s v="Elena"/>
+    <x v="13"/>
+    <x v="3"/>
+    <s v="Support Agent"/>
+    <s v="Female"/>
+    <n v="53"/>
+    <s v="2022-11-26"/>
+    <m/>
+    <s v="Active"/>
+    <n v="37583"/>
+    <n v="2"/>
+    <n v="3.6712328767123288"/>
+  </r>
+  <r>
+    <s v="E1128"/>
+    <s v="David"/>
+    <x v="2"/>
+    <x v="4"/>
+    <s v="HR Coordinator"/>
+    <s v="Male"/>
+    <n v="45"/>
+    <s v="2017-02-10"/>
+    <m/>
+    <s v="Active"/>
+    <n v="45920"/>
+    <n v="5"/>
+    <n v="9.4657534246575334"/>
+  </r>
+  <r>
+    <s v="E1129"/>
+    <s v="Max"/>
+    <x v="6"/>
+    <x v="5"/>
+    <s v="Software Engineer"/>
+    <s v="Male"/>
+    <n v="29"/>
+    <s v="2025-07-05"/>
+    <m/>
+    <s v="Active"/>
+    <n v="63501"/>
+    <n v="4"/>
+    <n v="1.0630136986301371"/>
+  </r>
+  <r>
+    <s v="E1130"/>
+    <s v="Anna"/>
+    <x v="3"/>
+    <x v="0"/>
+    <s v="Marketing Specialist"/>
+    <s v="Female"/>
+    <n v="58"/>
+    <s v="2018-04-20"/>
+    <m/>
+    <s v="Active"/>
+    <n v="51080"/>
+    <n v="3"/>
+    <n v="8.2767123287671236"/>
+  </r>
+  <r>
+    <s v="E1131"/>
+    <s v="Sofia"/>
+    <x v="11"/>
+    <x v="5"/>
+    <s v="Software Engineer"/>
+    <s v="Female"/>
+    <n v="60"/>
+    <s v="2016-01-12"/>
+    <m/>
+    <s v="Active"/>
+    <n v="64370"/>
+    <n v="5"/>
+    <n v="10.547945205479452"/>
+  </r>
+  <r>
+    <s v="E1132"/>
+    <s v="Erik"/>
+    <x v="8"/>
+    <x v="1"/>
+    <s v="Sales Manager"/>
+    <s v="Male"/>
+    <n v="23"/>
+    <s v="2017-06-23"/>
+    <m/>
+    <s v="Active"/>
+    <n v="80869"/>
+    <n v="4"/>
+    <n v="9.1013698630136979"/>
+  </r>
+  <r>
+    <s v="E1133"/>
+    <s v="Clara"/>
+    <x v="3"/>
+    <x v="1"/>
+    <s v="Sales Rep"/>
+    <s v="Female"/>
+    <n v="38"/>
+    <s v="2016-08-02"/>
+    <m/>
+    <s v="Active"/>
+    <n v="45897"/>
+    <n v="3"/>
+    <n v="9.9917808219178088"/>
+  </r>
+  <r>
+    <s v="E1134"/>
+    <s v="Emma"/>
+    <x v="2"/>
+    <x v="6"/>
+    <s v="Operations Manager"/>
+    <s v="Female"/>
+    <n v="54"/>
+    <s v="2022-08-28"/>
+    <m/>
+    <s v="Active"/>
+    <n v="78405"/>
+    <n v="3"/>
+    <n v="3.9178082191780823"/>
+  </r>
+  <r>
+    <s v="E1135"/>
+    <s v="Lisa"/>
+    <x v="9"/>
+    <x v="5"/>
+    <s v="QA Engineer"/>
+    <s v="Female"/>
+    <n v="23"/>
+    <s v="2016-09-06"/>
+    <m/>
+    <s v="Active"/>
+    <n v="55580"/>
+    <n v="3"/>
+    <n v="9.8958904109589039"/>
+  </r>
+  <r>
+    <s v="E1136"/>
+    <s v="Emma"/>
+    <x v="2"/>
+    <x v="1"/>
+    <s v="Sales Rep"/>
+    <s v="Female"/>
+    <n v="42"/>
+    <s v="2022-10-27"/>
+    <m/>
+    <s v="Active"/>
+    <n v="40076"/>
+    <n v="2"/>
+    <n v="3.7534246575342465"/>
+  </r>
+  <r>
+    <s v="E1137"/>
+    <s v="Tim"/>
+    <x v="14"/>
+    <x v="2"/>
+    <s v="Accountant"/>
+    <s v="Male"/>
+    <n v="51"/>
+    <s v="2021-09-01"/>
+    <s v="2024-02-29"/>
+    <s v="Terminated"/>
+    <n v="48624"/>
+    <n v="4"/>
+    <n v="4.9068493150684933"/>
+  </r>
+  <r>
+    <s v="E1138"/>
+    <s v="Sofia"/>
+    <x v="15"/>
+    <x v="3"/>
+    <s v="Support Agent"/>
+    <s v="Female"/>
+    <n v="49"/>
+    <s v="2021-01-23"/>
+    <m/>
+    <s v="Active"/>
+    <n v="39779"/>
+    <n v="3"/>
+    <n v="5.5123287671232877"/>
+  </r>
+  <r>
+    <s v="E1139"/>
+    <s v="Tim"/>
+    <x v="13"/>
+    <x v="3"/>
+    <s v="Support Agent"/>
+    <s v="Male"/>
+    <n v="42"/>
+    <s v="2020-10-14"/>
+    <m/>
+    <s v="Active"/>
+    <n v="43897"/>
+    <n v="3"/>
+    <n v="5.7890410958904113"/>
+  </r>
+  <r>
+    <s v="E1140"/>
+    <s v="Hannah"/>
+    <x v="10"/>
+    <x v="1"/>
+    <s v="Sales Rep"/>
+    <s v="Female"/>
+    <n v="27"/>
+    <s v="2017-01-16"/>
+    <m/>
+    <s v="Active"/>
+    <n v="40582"/>
+    <n v="4"/>
+    <n v="9.5342465753424666"/>
+  </r>
+  <r>
+    <s v="E1141"/>
+    <s v="Erik"/>
+    <x v="17"/>
+    <x v="2"/>
+    <s v="Financial Analyst"/>
+    <s v="Male"/>
+    <n v="59"/>
+    <s v="2022-04-19"/>
+    <s v="2024-03-24"/>
+    <s v="Terminated"/>
+    <n v="65977"/>
+    <n v="2"/>
+    <n v="4.2767123287671236"/>
+  </r>
+  <r>
+    <s v="E1142"/>
+    <s v="Simon"/>
+    <x v="13"/>
+    <x v="6"/>
+    <s v="Operations Analyst"/>
+    <s v="Male"/>
+    <n v="40"/>
+    <s v="2022-09-25"/>
+    <m/>
+    <s v="Active"/>
+    <n v="52761"/>
+    <n v="2"/>
+    <n v="3.8410958904109589"/>
+  </r>
+  <r>
+    <s v="E1143"/>
+    <s v="Laura"/>
+    <x v="10"/>
+    <x v="0"/>
+    <s v="Marketing Specialist"/>
+    <s v="Female"/>
+    <n v="44"/>
+    <s v="2025-06-24"/>
+    <s v="2026-01-28"/>
+    <s v="Terminated"/>
+    <n v="43882"/>
+    <n v="4"/>
+    <n v="1.0931506849315069"/>
+  </r>
+  <r>
+    <s v="E1144"/>
+    <s v="Mia"/>
+    <x v="13"/>
+    <x v="6"/>
+    <s v="Operations Analyst"/>
+    <s v="Female"/>
+    <n v="60"/>
+    <s v="2023-05-18"/>
+    <m/>
+    <s v="Active"/>
+    <n v="47474"/>
+    <n v="3"/>
+    <n v="3.1972602739726028"/>
+  </r>
+  <r>
+    <s v="E1145"/>
+    <s v="Finn"/>
+    <x v="3"/>
+    <x v="5"/>
+    <s v="Software Engineer"/>
+    <s v="Male"/>
+    <n v="33"/>
+    <s v="2025-10-02"/>
+    <m/>
+    <s v="Active"/>
+    <n v="71278"/>
+    <n v="4"/>
+    <n v="0.81917808219178079"/>
+  </r>
+  <r>
+    <s v="E1146"/>
+    <s v="Laura"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="Sales Manager"/>
+    <s v="Female"/>
+    <n v="55"/>
+    <s v="2018-05-31"/>
+    <m/>
+    <s v="Active"/>
+    <n v="81878"/>
+    <n v="3"/>
+    <n v="8.1643835616438363"/>
+  </r>
+  <r>
+    <s v="E1147"/>
+    <s v="Julia"/>
+    <x v="18"/>
+    <x v="3"/>
+    <s v="Support Team Lead"/>
+    <s v="Female"/>
+    <n v="58"/>
+    <s v="2022-09-08"/>
+    <m/>
+    <s v="Active"/>
+    <n v="43861"/>
+    <n v="3"/>
+    <n v="3.8876712328767122"/>
+  </r>
+  <r>
+    <s v="E1148"/>
+    <s v="Hannah"/>
+    <x v="12"/>
+    <x v="5"/>
+    <s v="QA Engineer"/>
+    <s v="Female"/>
+    <n v="49"/>
+    <s v="2021-06-12"/>
+    <s v="2024-01-03"/>
+    <s v="Terminated"/>
+    <n v="55785"/>
+    <n v="3"/>
+    <n v="5.1287671232876715"/>
+  </r>
+  <r>
+    <s v="E1149"/>
+    <s v="Julia"/>
+    <x v="13"/>
+    <x v="1"/>
+    <s v="Account Executive"/>
+    <s v="Female"/>
+    <n v="59"/>
+    <s v="2021-06-16"/>
+    <s v="2025-04-12"/>
+    <s v="Terminated"/>
+    <n v="57053"/>
+    <n v="2"/>
+    <n v="5.117808219178082"/>
+  </r>
+  <r>
+    <s v="E1150"/>
+    <s v="Tom"/>
+    <x v="16"/>
+    <x v="1"/>
+    <s v="Sales Rep"/>
+    <s v="Male"/>
+    <n v="41"/>
+    <s v="2018-05-15"/>
+    <m/>
+    <s v="Active"/>
+    <n v="43186"/>
+    <n v="3"/>
+    <n v="8.2082191780821923"/>
+  </r>
+  <r>
+    <s v="E1151"/>
+    <s v="Anna"/>
+    <x v="10"/>
+    <x v="3"/>
+    <s v="Support Team Lead"/>
+    <s v="Female"/>
+    <n v="33"/>
+    <s v="2017-06-13"/>
+    <m/>
+    <s v="Active"/>
+    <n v="51725"/>
+    <n v="4"/>
+    <n v="9.1287671232876715"/>
+  </r>
+  <r>
+    <s v="E1152"/>
+    <s v="Paul"/>
+    <x v="6"/>
+    <x v="6"/>
+    <s v="Operations Analyst"/>
+    <s v="Male"/>
+    <n v="49"/>
+    <s v="2016-03-17"/>
+    <m/>
+    <s v="Active"/>
+    <n v="48275"/>
+    <n v="5"/>
+    <n v="10.36986301369863"/>
+  </r>
+  <r>
+    <s v="E1153"/>
+    <s v="Tom"/>
+    <x v="6"/>
+    <x v="3"/>
+    <s v="Support Team Lead"/>
+    <s v="Male"/>
+    <n v="40"/>
+    <s v="2017-04-16"/>
+    <m/>
+    <s v="Active"/>
+    <n v="43341"/>
+    <n v="5"/>
+    <n v="9.287671232876713"/>
+  </r>
+  <r>
+    <s v="E1154"/>
+    <s v="Mia"/>
+    <x v="14"/>
+    <x v="4"/>
+    <s v="HR Manager"/>
+    <s v="Female"/>
+    <n v="45"/>
+    <s v="2016-12-26"/>
+    <m/>
+    <s v="Active"/>
+    <n v="68734"/>
+    <n v="3"/>
+    <n v="9.5917808219178085"/>
+  </r>
+  <r>
+    <s v="E1155"/>
+    <s v="Jan"/>
+    <x v="12"/>
+    <x v="4"/>
+    <s v="Recruiter"/>
+    <s v="Male"/>
+    <n v="43"/>
+    <s v="2018-06-26"/>
+    <m/>
+    <s v="Active"/>
+    <n v="47754"/>
+    <n v="2"/>
+    <n v="8.0931506849315067"/>
+  </r>
+  <r>
+    <s v="E1156"/>
+    <s v="Lea"/>
+    <x v="9"/>
+    <x v="0"/>
+    <s v="Content Strategist"/>
+    <s v="Female"/>
+    <n v="44"/>
+    <s v="2024-02-27"/>
+    <m/>
+    <s v="Active"/>
+    <n v="47871"/>
+    <n v="2"/>
+    <n v="2.4164383561643836"/>
+  </r>
+  <r>
+    <s v="E1157"/>
+    <s v="David"/>
+    <x v="8"/>
+    <x v="2"/>
+    <s v="Financial Analyst"/>
+    <s v="Male"/>
+    <n v="26"/>
+    <s v="2017-12-26"/>
+    <m/>
+    <s v="Active"/>
+    <n v="62601"/>
+    <n v="4"/>
+    <n v="8.5917808219178085"/>
+  </r>
+  <r>
+    <s v="E1158"/>
+    <s v="Noah"/>
+    <x v="7"/>
+    <x v="3"/>
+    <s v="Support Team Lead"/>
+    <s v="Male"/>
+    <n v="42"/>
+    <s v="2017-09-10"/>
+    <m/>
+    <s v="Active"/>
+    <n v="44118"/>
+    <n v="3"/>
+    <n v="8.8849315068493144"/>
+  </r>
+  <r>
+    <s v="E1159"/>
+    <s v="Erik"/>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="Financial Analyst"/>
+    <s v="Male"/>
+    <n v="44"/>
+    <s v="2021-09-09"/>
+    <m/>
+    <s v="Active"/>
+    <n v="60085"/>
+    <n v="3"/>
+    <n v="4.8849315068493153"/>
+  </r>
+  <r>
+    <s v="E1160"/>
+    <s v="Anna"/>
+    <x v="19"/>
+    <x v="6"/>
+    <s v="Operations Manager"/>
+    <s v="Female"/>
+    <n v="26"/>
+    <s v="2023-03-25"/>
+    <m/>
+    <s v="Active"/>
+    <n v="81076"/>
+    <n v="4"/>
+    <n v="3.3452054794520549"/>
+  </r>
+  <r>
+    <s v="E1161"/>
+    <s v="Leon"/>
+    <x v="7"/>
+    <x v="2"/>
+    <s v="Finance Manager"/>
+    <s v="Male"/>
+    <n v="24"/>
+    <s v="2021-01-16"/>
+    <s v="2024-10-11"/>
+    <s v="Terminated"/>
+    <n v="80084"/>
+    <n v="3"/>
+    <n v="5.5315068493150683"/>
+  </r>
+  <r>
+    <s v="E1162"/>
+    <s v="Jan"/>
+    <x v="17"/>
+    <x v="1"/>
+    <s v="Account Executive"/>
+    <s v="Male"/>
+    <n v="28"/>
+    <s v="2025-02-03"/>
+    <m/>
+    <s v="Active"/>
+    <n v="53381"/>
+    <n v="3"/>
+    <n v="1.4794520547945205"/>
+  </r>
+  <r>
+    <s v="E1163"/>
+    <s v="Anna"/>
+    <x v="11"/>
+    <x v="3"/>
+    <s v="Support Team Lead"/>
+    <s v="Female"/>
+    <n v="50"/>
+    <s v="2021-11-16"/>
+    <s v="2025-05-17"/>
+    <s v="Terminated"/>
+    <n v="45600"/>
+    <n v="3"/>
+    <n v="4.6986301369863011"/>
+  </r>
+  <r>
+    <s v="E1164"/>
+    <s v="Tim"/>
+    <x v="13"/>
+    <x v="6"/>
+    <s v="Operations Manager"/>
+    <s v="Male"/>
+    <n v="60"/>
+    <s v="2016-08-02"/>
+    <m/>
+    <s v="Active"/>
+    <n v="72079"/>
+    <n v="3"/>
+    <n v="9.9917808219178088"/>
+  </r>
+  <r>
+    <s v="E1165"/>
+    <s v="Jonas"/>
+    <x v="0"/>
+    <x v="3"/>
+    <s v="Support Agent"/>
+    <s v="Male"/>
+    <n v="43"/>
+    <s v="2016-11-29"/>
+    <s v="2024-06-08"/>
+    <s v="Terminated"/>
+    <n v="35317"/>
+    <n v="5"/>
+    <n v="9.6657534246575345"/>
+  </r>
+  <r>
+    <s v="E1166"/>
+    <s v="Noah"/>
+    <x v="6"/>
+    <x v="0"/>
+    <s v="Marketing Manager"/>
+    <s v="Male"/>
+    <n v="27"/>
+    <s v="2019-06-22"/>
+    <s v="2023-10-11"/>
+    <s v="Terminated"/>
+    <n v="82542"/>
+    <n v="4"/>
+    <n v="7.1041095890410961"/>
+  </r>
+  <r>
+    <s v="E1167"/>
+    <s v="Hannah"/>
+    <x v="9"/>
+    <x v="1"/>
+    <s v="Sales Manager"/>
+    <s v="Female"/>
+    <n v="49"/>
+    <s v="2021-09-13"/>
+    <m/>
+    <s v="Active"/>
+    <n v="75298"/>
+    <n v="3"/>
+    <n v="4.8739726027397259"/>
+  </r>
+  <r>
+    <s v="E1168"/>
+    <s v="Sophie"/>
+    <x v="3"/>
+    <x v="6"/>
+    <s v="Operations Manager"/>
+    <s v="Female"/>
+    <n v="34"/>
+    <s v="2018-07-16"/>
+    <m/>
+    <s v="Active"/>
+    <n v="73538"/>
+    <n v="2"/>
+    <n v="8.0383561643835613"/>
+  </r>
+  <r>
+    <s v="E1169"/>
+    <s v="Lea"/>
+    <x v="15"/>
+    <x v="6"/>
+    <s v="Operations Analyst"/>
+    <s v="Female"/>
+    <n v="43"/>
+    <s v="2025-10-29"/>
+    <s v="2025-12-31"/>
+    <s v="Terminated"/>
+    <n v="56785"/>
+    <n v="3"/>
+    <n v="0.74520547945205484"/>
+  </r>
+  <r>
+    <s v="E1170"/>
+    <s v="Laura"/>
+    <x v="14"/>
+    <x v="6"/>
+    <s v="Operations Analyst"/>
+    <s v="Female"/>
+    <n v="50"/>
+    <s v="2016-06-27"/>
+    <m/>
+    <s v="Active"/>
+    <n v="52968"/>
+    <n v="4"/>
+    <n v="10.09041095890411"/>
+  </r>
+  <r>
+    <s v="E1171"/>
+    <s v="Emma"/>
+    <x v="14"/>
+    <x v="5"/>
+    <s v="Engineering Manager"/>
+    <s v="Female"/>
+    <n v="50"/>
+    <s v="2018-08-16"/>
+    <s v="2021-05-21"/>
+    <s v="Terminated"/>
+    <n v="94070"/>
+    <n v="5"/>
+    <n v="7.9534246575342467"/>
+  </r>
+  <r>
+    <s v="E1172"/>
+    <s v="Finn"/>
+    <x v="4"/>
+    <x v="5"/>
+    <s v="Engineering Manager"/>
+    <s v="Male"/>
+    <n v="58"/>
+    <s v="2020-12-09"/>
+    <m/>
+    <s v="Active"/>
+    <n v="93616"/>
+    <n v="4"/>
+    <n v="5.6356164383561644"/>
+  </r>
+  <r>
+    <s v="E1173"/>
+    <s v="Lukas"/>
+    <x v="4"/>
+    <x v="6"/>
+    <s v="Operations Analyst"/>
+    <s v="Male"/>
+    <n v="38"/>
+    <s v="2016-08-01"/>
+    <m/>
+    <s v="Active"/>
+    <n v="53081"/>
+    <n v="4"/>
+    <n v="9.9945205479452053"/>
+  </r>
+  <r>
+    <s v="E1174"/>
+    <s v="Lisa"/>
+    <x v="9"/>
+    <x v="6"/>
+    <s v="Operations Analyst"/>
+    <s v="Female"/>
+    <n v="40"/>
+    <s v="2016-12-09"/>
+    <m/>
+    <s v="Active"/>
+    <n v="51469"/>
+    <n v="3"/>
+    <n v="9.6383561643835609"/>
+  </r>
+  <r>
+    <s v="E1175"/>
+    <s v="Sofia"/>
+    <x v="13"/>
+    <x v="1"/>
+    <s v="Sales Rep"/>
+    <s v="Female"/>
+    <n v="50"/>
+    <s v="2025-12-02"/>
+    <m/>
+    <s v="Active"/>
+    <n v="39436"/>
+    <n v="3"/>
+    <n v="0.65205479452054793"/>
+  </r>
+  <r>
+    <s v="E1176"/>
+    <s v="Jan"/>
+    <x v="19"/>
+    <x v="0"/>
+    <s v="Content Strategist"/>
+    <s v="Male"/>
+    <n v="27"/>
+    <s v="2020-03-15"/>
+    <m/>
+    <s v="Active"/>
+    <n v="44461"/>
+    <n v="3"/>
+    <n v="6.3726027397260276"/>
+  </r>
+  <r>
+    <s v="E1177"/>
+    <s v="Sofia"/>
+    <x v="3"/>
+    <x v="6"/>
+    <s v="Operations Analyst"/>
+    <s v="Female"/>
+    <n v="30"/>
+    <s v="2016-06-05"/>
+    <m/>
+    <s v="Active"/>
+    <n v="54740"/>
+    <n v="4"/>
+    <n v="10.150684931506849"/>
+  </r>
+  <r>
+    <s v="E1178"/>
+    <s v="Mia"/>
+    <x v="10"/>
+    <x v="4"/>
+    <s v="HR Manager"/>
+    <s v="Female"/>
+    <n v="22"/>
+    <s v="2016-11-20"/>
+    <m/>
+    <s v="Active"/>
+    <n v="71193"/>
+    <n v="3"/>
+    <n v="9.6904109589041099"/>
+  </r>
+  <r>
+    <s v="E1179"/>
+    <s v="Lea"/>
+    <x v="14"/>
+    <x v="2"/>
+    <s v="Accountant"/>
+    <s v="Female"/>
+    <n v="29"/>
+    <s v="2024-09-14"/>
+    <m/>
+    <s v="Active"/>
+    <n v="50893"/>
+    <n v="3"/>
+    <n v="1.8684931506849316"/>
+  </r>
+  <r>
+    <s v="E1180"/>
+    <s v="Sophie"/>
+    <x v="13"/>
+    <x v="3"/>
+    <s v="Support Team Lead"/>
+    <s v="Female"/>
+    <n v="26"/>
+    <s v="2017-03-30"/>
+    <m/>
+    <s v="Active"/>
+    <n v="52776"/>
+    <n v="4"/>
+    <n v="9.3342465753424655"/>
+  </r>
+  <r>
+    <s v="E1181"/>
+    <s v="Lisa"/>
+    <x v="17"/>
+    <x v="5"/>
+    <s v="QA Engineer"/>
+    <s v="Female"/>
+    <n v="22"/>
+    <s v="2022-11-23"/>
+    <m/>
+    <s v="Active"/>
+    <n v="52941"/>
+    <n v="4"/>
+    <n v="3.6794520547945204"/>
+  </r>
+  <r>
+    <s v="E1182"/>
+    <s v="Hannah"/>
+    <x v="12"/>
+    <x v="2"/>
+    <s v="Accountant"/>
+    <s v="Female"/>
+    <n v="26"/>
+    <s v="2021-11-24"/>
+    <s v="2024-10-28"/>
+    <s v="Terminated"/>
+    <n v="55316"/>
+    <n v="4"/>
+    <n v="4.6767123287671231"/>
+  </r>
+  <r>
+    <s v="E1183"/>
+    <s v="Simon"/>
+    <x v="10"/>
+    <x v="1"/>
+    <s v="Sales Manager"/>
+    <s v="Male"/>
+    <n v="46"/>
+    <s v="2020-03-09"/>
+    <m/>
+    <s v="Active"/>
+    <n v="75266"/>
+    <n v="3"/>
+    <n v="6.3890410958904109"/>
+  </r>
+  <r>
+    <s v="E1184"/>
+    <s v="Julia"/>
+    <x v="11"/>
+    <x v="3"/>
+    <s v="Support Agent"/>
+    <s v="Female"/>
+    <n v="59"/>
+    <s v="2024-03-30"/>
+    <m/>
+    <s v="Active"/>
+    <n v="35185"/>
+    <n v="2"/>
+    <n v="2.3287671232876712"/>
+  </r>
+  <r>
+    <s v="E1185"/>
+    <s v="Simon"/>
+    <x v="8"/>
+    <x v="6"/>
+    <s v="Operations Manager"/>
+    <s v="Male"/>
+    <n v="52"/>
+    <s v="2023-01-31"/>
+    <m/>
+    <s v="Active"/>
+    <n v="73209"/>
+    <n v="2"/>
+    <n v="3.4904109589041097"/>
+  </r>
+  <r>
+    <s v="E1186"/>
+    <s v="Max"/>
+    <x v="18"/>
+    <x v="0"/>
+    <s v="Marketing Specialist"/>
+    <s v="Male"/>
+    <n v="34"/>
+    <s v="2025-12-07"/>
+    <m/>
+    <s v="Active"/>
+    <n v="47170"/>
+    <n v="5"/>
+    <n v="0.63835616438356169"/>
+  </r>
+  <r>
+    <s v="E1187"/>
+    <s v="Simon"/>
+    <x v="15"/>
+    <x v="4"/>
+    <s v="Recruiter"/>
+    <s v="Male"/>
+    <n v="24"/>
+    <s v="2024-06-12"/>
+    <m/>
+    <s v="Active"/>
+    <n v="49687"/>
+    <n v="3"/>
+    <n v="2.1260273972602741"/>
+  </r>
+  <r>
+    <s v="E1188"/>
+    <s v="Sofia"/>
+    <x v="3"/>
+    <x v="5"/>
+    <s v="Software Engineer"/>
+    <s v="Female"/>
+    <n v="45"/>
+    <s v="2020-11-24"/>
+    <m/>
+    <s v="Active"/>
+    <n v="69204"/>
+    <n v="5"/>
+    <n v="5.6767123287671231"/>
+  </r>
+  <r>
+    <s v="E1189"/>
+    <s v="Felix"/>
+    <x v="8"/>
+    <x v="4"/>
+    <s v="HR Manager"/>
+    <s v="Male"/>
+    <n v="53"/>
+    <s v="2020-02-13"/>
+    <s v="2023-03-11"/>
+    <s v="Terminated"/>
+    <n v="68353"/>
+    <n v="4"/>
+    <n v="6.4575342465753423"/>
+  </r>
+  <r>
+    <s v="E1190"/>
+    <s v="Sarah"/>
+    <x v="14"/>
+    <x v="6"/>
+    <s v="Operations Analyst"/>
+    <s v="Female"/>
+    <n v="56"/>
+    <s v="2019-04-18"/>
+    <m/>
+    <s v="Active"/>
+    <n v="48680"/>
+    <n v="2"/>
+    <n v="7.2821917808219174"/>
+  </r>
+  <r>
+    <s v="E1191"/>
+    <s v="Jonas"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Finance Manager"/>
+    <s v="Male"/>
+    <n v="49"/>
+    <s v="2017-11-13"/>
+    <m/>
+    <s v="Active"/>
+    <n v="82759"/>
+    <n v="3"/>
+    <n v="8.7095890410958905"/>
+  </r>
+  <r>
+    <s v="E1192"/>
+    <s v="Tom"/>
+    <x v="13"/>
+    <x v="5"/>
+    <s v="Engineering Manager"/>
+    <s v="Male"/>
+    <n v="25"/>
+    <s v="2016-11-03"/>
+    <m/>
+    <s v="Active"/>
+    <n v="94952"/>
+    <n v="3"/>
+    <n v="9.7369863013698623"/>
+  </r>
+  <r>
+    <s v="E1193"/>
+    <s v="Anna"/>
+    <x v="17"/>
+    <x v="6"/>
+    <s v="Operations Manager"/>
+    <s v="Female"/>
+    <n v="24"/>
+    <s v="2017-06-01"/>
+    <m/>
+    <s v="Active"/>
+    <n v="74866"/>
+    <n v="4"/>
+    <n v="9.161643835616438"/>
+  </r>
+  <r>
+    <s v="E1194"/>
+    <s v="Felix"/>
+    <x v="6"/>
+    <x v="2"/>
+    <s v="Financial Analyst"/>
+    <s v="Male"/>
+    <n v="60"/>
+    <s v="2017-09-20"/>
+    <m/>
+    <s v="Active"/>
+    <n v="61077"/>
+    <n v="3"/>
+    <n v="8.8575342465753426"/>
+  </r>
+  <r>
+    <s v="E1195"/>
+    <s v="Clara"/>
+    <x v="17"/>
+    <x v="2"/>
+    <s v="Accountant"/>
+    <s v="Female"/>
+    <n v="47"/>
+    <s v="2019-07-11"/>
+    <m/>
+    <s v="Active"/>
+    <n v="51089"/>
+    <n v="5"/>
+    <n v="7.0520547945205481"/>
+  </r>
+  <r>
+    <s v="E1196"/>
+    <s v="Lisa"/>
+    <x v="8"/>
+    <x v="4"/>
+    <s v="HR Manager"/>
+    <s v="Female"/>
+    <n v="46"/>
+    <s v="2022-04-19"/>
+    <m/>
+    <s v="Active"/>
+    <n v="71288"/>
+    <n v="4"/>
+    <n v="4.2767123287671236"/>
+  </r>
+  <r>
+    <s v="E1197"/>
+    <s v="David"/>
+    <x v="14"/>
+    <x v="5"/>
+    <s v="Engineering Manager"/>
+    <s v="Male"/>
+    <n v="53"/>
+    <s v="2018-03-30"/>
+    <m/>
+    <s v="Active"/>
+    <n v="91223"/>
+    <n v="5"/>
+    <n v="8.3342465753424655"/>
+  </r>
+  <r>
+    <s v="E1198"/>
+    <s v="Lukas"/>
+    <x v="2"/>
+    <x v="1"/>
+    <s v="Sales Manager"/>
+    <s v="Male"/>
+    <n v="42"/>
+    <s v="2023-06-28"/>
+    <m/>
+    <s v="Active"/>
+    <n v="76063"/>
+    <n v="4"/>
+    <n v="3.0849315068493151"/>
+  </r>
+  <r>
+    <s v="E1199"/>
+    <s v="Finn"/>
+    <x v="18"/>
+    <x v="6"/>
+    <s v="Operations Analyst"/>
+    <s v="Male"/>
+    <n v="33"/>
+    <s v="2024-11-24"/>
+    <m/>
+    <s v="Active"/>
+    <n v="55335"/>
+    <n v="3"/>
+    <n v="1.6739726027397259"/>
+  </r>
+  <r>
+    <s v="E1200"/>
+    <s v="Mia"/>
+    <x v="17"/>
+    <x v="0"/>
+    <s v="Content Strategist"/>
+    <s v="Female"/>
+    <n v="23"/>
+    <s v="2020-01-18"/>
+    <s v="2026-07-19"/>
+    <s v="Terminated"/>
+    <n v="50044"/>
+    <n v="3"/>
+    <n v="6.5287671232876709"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+  <location ref="D1:E3" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="13">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="21">
+        <item x="19"/>
+        <item x="11"/>
+        <item x="7"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="13"/>
+        <item x="3"/>
+        <item x="14"/>
+        <item x="8"/>
+        <item x="1"/>
+        <item x="10"/>
+        <item x="6"/>
+        <item x="18"/>
+        <item x="16"/>
+        <item x="12"/>
+        <item x="9"/>
+        <item x="4"/>
+        <item x="17"/>
+        <item x="2"/>
+        <item x="15"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0" sortType="ascending">
+      <items count="8">
+        <item h="1" x="3"/>
+        <item h="1" x="5"/>
+        <item h="1" x="2"/>
+        <item h="1" x="4"/>
+        <item h="1" x="0"/>
+        <item h="1" x="6"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x v="6"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of AnnualSalary" fld="10" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x" name="Slicer_Department" sourceName="Department">
+  <pivotTables>
+    <pivotTable tabId="2" name="PivotTable1"/>
+  </pivotTables>
+  <data>
+    <tabular pivotCacheId="1">
+      <items count="7">
+        <i x="3"/>
+        <i x="5"/>
+        <i x="2"/>
+        <i x="4"/>
+        <i x="0"/>
+        <i x="6"/>
+        <i x="1" s="1"/>
+      </items>
+    </tabular>
+  </data>
+</slicerCacheDefinition>
+</file>
+
+<file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
+<slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <slicer name="Department" cache="Slicer_Department" caption="Department" rowHeight="241300"/>
+</slicers>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:M201" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:M201" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
   <autoFilter ref="A1:M201"/>
   <tableColumns count="13">
-    <tableColumn id="1" name="EmployeeID" dataDxfId="13"/>
-    <tableColumn id="2" name="FirstName" dataDxfId="12"/>
-    <tableColumn id="3" name="LastName" dataDxfId="11"/>
-    <tableColumn id="4" name="Department" dataDxfId="10"/>
-    <tableColumn id="5" name="JobTitle" dataDxfId="9"/>
-    <tableColumn id="6" name="Gender" dataDxfId="8"/>
-    <tableColumn id="7" name="Age" dataDxfId="7"/>
-    <tableColumn id="8" name="HireDate" dataDxfId="6"/>
-    <tableColumn id="9" name="TerminationDate" dataDxfId="5"/>
-    <tableColumn id="10" name="EmploymentStatus" dataDxfId="4"/>
-    <tableColumn id="11" name="AnnualSalary" dataDxfId="3"/>
-    <tableColumn id="12" name="PerformanceRating" dataDxfId="2"/>
+    <tableColumn id="1" name="EmployeeID" dataDxfId="11"/>
+    <tableColumn id="2" name="FirstName" dataDxfId="10"/>
+    <tableColumn id="3" name="LastName" dataDxfId="9"/>
+    <tableColumn id="4" name="Department" dataDxfId="8"/>
+    <tableColumn id="5" name="JobTitle" dataDxfId="7"/>
+    <tableColumn id="6" name="Gender" dataDxfId="6"/>
+    <tableColumn id="7" name="Age" dataDxfId="5"/>
+    <tableColumn id="8" name="HireDate" dataDxfId="4"/>
+    <tableColumn id="9" name="TerminationDate" dataDxfId="3"/>
+    <tableColumn id="10" name="EmploymentStatus" dataDxfId="2"/>
+    <tableColumn id="11" name="AnnualSalary" dataDxfId="1"/>
+    <tableColumn id="12" name="PerformanceRating" dataDxfId="0"/>
     <tableColumn id="13" name="TenureYears">
       <calculatedColumnFormula>(TODAY()-H2)/365</calculatedColumnFormula>
     </tableColumn>
@@ -10382,4 +16448,149 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" customWidth="1"/>
+    <col min="4" max="4" width="14.140625" customWidth="1"/>
+    <col min="5" max="5" width="20" customWidth="1"/>
+    <col min="6" max="6" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="25.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="10" t="s">
+        <v>527</v>
+      </c>
+      <c r="B1" s="6">
+        <f>COUNTIFS(Table1[EmploymentStatus],"Active")</f>
+        <v>156</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="E1" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="25.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="10" t="s">
+        <v>528</v>
+      </c>
+      <c r="B2" s="8">
+        <f>COUNTIFS(Table1[EmploymentStatus],"Terminated")/COUNTA(Table1[EmployeeID])</f>
+        <v>0.22</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="5">
+        <v>1901625</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D3" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="E3" s="5">
+        <v>1901625</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="25.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="10" t="s">
+        <v>532</v>
+      </c>
+      <c r="B4" s="7">
+        <f ca="1">AVERAGEIFS(Table1[TenureYears],Table1[EmploymentStatus],"Active")</f>
+        <v>5.7536354056901997</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="25.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="10" t="s">
+        <v>533</v>
+      </c>
+      <c r="B6" s="9">
+        <f>COUNTIFS(Table1[Gender],"Female",Table1[EmploymentStatus],"Active")/$B$1</f>
+        <v>0.50641025641025639</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="25.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="11" t="s">
+        <v>534</v>
+      </c>
+      <c r="B7" s="9">
+        <f>COUNTIFS(Table1[Gender],"Male",Table1[EmploymentStatus],"Active")/$B$1</f>
+        <v>0.49358974358974361</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>535</v>
+      </c>
+      <c r="B9" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="B10">
+        <f>COUNTIFS(Table1[PerformanceRating],A10)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>2</v>
+      </c>
+      <c r="B11">
+        <f>COUNTIFS(Table1[PerformanceRating],A11)</f>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>3</v>
+      </c>
+      <c r="B12">
+        <f>COUNTIFS(Table1[PerformanceRating],A12)</f>
+        <v>77</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>4</v>
+      </c>
+      <c r="B13">
+        <f>COUNTIFS(Table1[PerformanceRating],A13)</f>
+        <v>63</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>5</v>
+      </c>
+      <c r="B14">
+        <f>COUNTIFS(Table1[PerformanceRating],A14)</f>
+        <v>32</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
+  <drawing r:id="rId3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{A8765BA9-456A-4dab-B4F3-ACF838C121DE}">
+      <x14:slicerList>
+        <x14:slicer r:id="rId4"/>
+      </x14:slicerList>
+    </ext>
+  </extLst>
+</worksheet>
 </file>
--- a/hr_employee_data.xlsx
+++ b/hr_employee_data.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr/>
+  <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\The Moor\Desktop\Project\hr-kpi-excel-dashboard\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\The Moor\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -20,7 +20,7 @@
   </definedNames>
   <calcPr calcId="152511"/>
   <pivotCaches>
-    <pivotCache cacheId="3" r:id="rId3"/>
+    <pivotCache cacheId="0" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -1654,8 +1654,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="2">
-    <numFmt numFmtId="168" formatCode="0.0%"/>
-    <numFmt numFmtId="173" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -1724,7 +1724,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1747,6 +1747,19 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1763,12 +1776,12 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="173" fontId="4" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="4" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2224,11 +2237,11 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="462644184"/>
-        <c:axId val="462644968"/>
+        <c:axId val="345475008"/>
+        <c:axId val="345475392"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="462644184"/>
+        <c:axId val="345475008"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2271,7 +2284,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="462644968"/>
+        <c:crossAx val="345475392"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2279,7 +2292,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="462644968"/>
+        <c:axId val="345475392"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2330,7 +2343,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="462644184"/>
+        <c:crossAx val="345475008"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2783,11 +2796,11 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="463018928"/>
-        <c:axId val="463016968"/>
+        <c:axId val="346758712"/>
+        <c:axId val="346764752"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="463018928"/>
+        <c:axId val="346758712"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2829,7 +2842,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="463016968"/>
+        <c:crossAx val="346764752"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2837,7 +2850,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="463016968"/>
+        <c:axId val="346764752"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2888,7 +2901,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="463018928"/>
+        <c:crossAx val="346758712"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4719,8 +4732,8 @@
       <xdr:row>29</xdr:row>
       <xdr:rowOff>2381</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="5" name="Department"/>
@@ -4737,7 +4750,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -7870,7 +7883,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="D1:E3" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="13">
     <pivotField showAll="0"/>
@@ -8391,7 +8404,7 @@
       </c>
       <c r="M2">
         <f ca="1">(TODAY()-H2)/365</f>
-        <v>2.3150684931506849</v>
+        <v>2.3452054794520549</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
@@ -8433,7 +8446,7 @@
       </c>
       <c r="M3">
         <f t="shared" ref="M3:M66" ca="1" si="0">(TODAY()-H3)/365</f>
-        <v>4.9095890410958907</v>
+        <v>4.9397260273972599</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
@@ -8473,7 +8486,7 @@
       </c>
       <c r="M4">
         <f t="shared" ca="1" si="0"/>
-        <v>2.0630136986301371</v>
+        <v>2.0931506849315067</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
@@ -8513,7 +8526,7 @@
       </c>
       <c r="M5">
         <f t="shared" ca="1" si="0"/>
-        <v>9.493150684931507</v>
+        <v>9.5232876712328771</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
@@ -8555,7 +8568,7 @@
       </c>
       <c r="M6">
         <f t="shared" ca="1" si="0"/>
-        <v>9.6958904109589046</v>
+        <v>9.7260273972602747</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
@@ -8595,7 +8608,7 @@
       </c>
       <c r="M7">
         <f t="shared" ca="1" si="0"/>
-        <v>3.1589041095890411</v>
+        <v>3.1890410958904107</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
@@ -8635,7 +8648,7 @@
       </c>
       <c r="M8">
         <f t="shared" ca="1" si="0"/>
-        <v>3.4465753424657533</v>
+        <v>3.4767123287671233</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
@@ -8675,7 +8688,7 @@
       </c>
       <c r="M9">
         <f t="shared" ca="1" si="0"/>
-        <v>3.4547945205479453</v>
+        <v>3.484931506849315</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
@@ -8715,7 +8728,7 @@
       </c>
       <c r="M10">
         <f t="shared" ca="1" si="0"/>
-        <v>8.1150684931506856</v>
+        <v>8.1452054794520556</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
@@ -8757,7 +8770,7 @@
       </c>
       <c r="M11">
         <f t="shared" ca="1" si="0"/>
-        <v>8.2109589041095887</v>
+        <v>8.2410958904109588</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
@@ -8799,7 +8812,7 @@
       </c>
       <c r="M12">
         <f t="shared" ca="1" si="0"/>
-        <v>7.8109589041095893</v>
+        <v>7.8410958904109593</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
@@ -8841,7 +8854,7 @@
       </c>
       <c r="M13">
         <f t="shared" ca="1" si="0"/>
-        <v>9.0273972602739718</v>
+        <v>9.0575342465753419</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
@@ -8881,7 +8894,7 @@
       </c>
       <c r="M14">
         <f t="shared" ca="1" si="0"/>
-        <v>9.8657534246575338</v>
+        <v>9.8958904109589039</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
@@ -8923,7 +8936,7 @@
       </c>
       <c r="M15">
         <f t="shared" ca="1" si="0"/>
-        <v>2.9287671232876713</v>
+        <v>2.9589041095890409</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
@@ -8963,7 +8976,7 @@
       </c>
       <c r="M16">
         <f t="shared" ca="1" si="0"/>
-        <v>4.9616438356164387</v>
+        <v>4.9917808219178079</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
@@ -9003,7 +9016,7 @@
       </c>
       <c r="M17">
         <f t="shared" ca="1" si="0"/>
-        <v>6.3835616438356162</v>
+        <v>6.4136986301369863</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
@@ -9043,7 +9056,7 @@
       </c>
       <c r="M18">
         <f t="shared" ca="1" si="0"/>
-        <v>6.506849315068493</v>
+        <v>6.536986301369863</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
@@ -9083,7 +9096,7 @@
       </c>
       <c r="M19">
         <f t="shared" ca="1" si="0"/>
-        <v>1.9863013698630136</v>
+        <v>2.0164383561643837</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
@@ -9123,7 +9136,7 @@
       </c>
       <c r="M20">
         <f t="shared" ca="1" si="0"/>
-        <v>4.5287671232876709</v>
+        <v>4.558904109589041</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
@@ -9163,7 +9176,7 @@
       </c>
       <c r="M21">
         <f t="shared" ca="1" si="0"/>
-        <v>8.0575342465753419</v>
+        <v>8.087671232876712</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
@@ -9203,7 +9216,7 @@
       </c>
       <c r="M22">
         <f t="shared" ca="1" si="0"/>
-        <v>8.0109589041095894</v>
+        <v>8.0410958904109595</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
@@ -9245,7 +9258,7 @@
       </c>
       <c r="M23">
         <f t="shared" ca="1" si="0"/>
-        <v>8.1753424657534239</v>
+        <v>8.205479452054794</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
@@ -9285,7 +9298,7 @@
       </c>
       <c r="M24">
         <f t="shared" ca="1" si="0"/>
-        <v>9.5205479452054789</v>
+        <v>9.5506849315068489</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
@@ -9325,7 +9338,7 @@
       </c>
       <c r="M25">
         <f t="shared" ca="1" si="0"/>
-        <v>9.8986301369863021</v>
+        <v>9.9287671232876704</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
@@ -9365,7 +9378,7 @@
       </c>
       <c r="M26">
         <f t="shared" ca="1" si="0"/>
-        <v>9.0054794520547947</v>
+        <v>9.0356164383561648</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
@@ -9407,7 +9420,7 @@
       </c>
       <c r="M27">
         <f t="shared" ca="1" si="0"/>
-        <v>10.010958904109589</v>
+        <v>10.04109589041096</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
@@ -9447,7 +9460,7 @@
       </c>
       <c r="M28">
         <f t="shared" ca="1" si="0"/>
-        <v>0.87671232876712324</v>
+        <v>0.9068493150684932</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
@@ -9489,7 +9502,7 @@
       </c>
       <c r="M29">
         <f t="shared" ca="1" si="0"/>
-        <v>5.8328767123287673</v>
+        <v>5.8630136986301373</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
@@ -9529,7 +9542,7 @@
       </c>
       <c r="M30">
         <f t="shared" ca="1" si="0"/>
-        <v>9.9369863013698634</v>
+        <v>9.9671232876712335</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
@@ -9569,7 +9582,7 @@
       </c>
       <c r="M31">
         <f t="shared" ca="1" si="0"/>
-        <v>3.9013698630136986</v>
+        <v>3.9315068493150687</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
@@ -9611,7 +9624,7 @@
       </c>
       <c r="M32">
         <f t="shared" ca="1" si="0"/>
-        <v>5.8739726027397259</v>
+        <v>5.904109589041096</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
@@ -9651,7 +9664,7 @@
       </c>
       <c r="M33">
         <f t="shared" ca="1" si="0"/>
-        <v>5.4493150684931511</v>
+        <v>5.4794520547945202</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
@@ -9691,7 +9704,7 @@
       </c>
       <c r="M34">
         <f t="shared" ca="1" si="0"/>
-        <v>9.0931506849315067</v>
+        <v>9.1232876712328768</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
@@ -9733,7 +9746,7 @@
       </c>
       <c r="M35">
         <f t="shared" ca="1" si="0"/>
-        <v>3.7150684931506848</v>
+        <v>3.7452054794520548</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.25">
@@ -9773,7 +9786,7 @@
       </c>
       <c r="M36">
         <f t="shared" ca="1" si="0"/>
-        <v>0.59452054794520548</v>
+        <v>0.62465753424657533</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
@@ -9813,7 +9826,7 @@
       </c>
       <c r="M37">
         <f t="shared" ca="1" si="0"/>
-        <v>2.8657534246575342</v>
+        <v>2.8958904109589043</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
@@ -9853,7 +9866,7 @@
       </c>
       <c r="M38">
         <f t="shared" ca="1" si="0"/>
-        <v>10.53972602739726</v>
+        <v>10.56986301369863</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
@@ -9893,7 +9906,7 @@
       </c>
       <c r="M39">
         <f t="shared" ca="1" si="0"/>
-        <v>4.2849315068493148</v>
+        <v>4.3150684931506849</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
@@ -9933,7 +9946,7 @@
       </c>
       <c r="M40">
         <f t="shared" ca="1" si="0"/>
-        <v>4.3780821917808215</v>
+        <v>4.4082191780821915</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
@@ -9973,7 +9986,7 @@
       </c>
       <c r="M41">
         <f t="shared" ca="1" si="0"/>
-        <v>3.095890410958904</v>
+        <v>3.1260273972602741</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.25">
@@ -10013,7 +10026,7 @@
       </c>
       <c r="M42">
         <f t="shared" ca="1" si="0"/>
-        <v>0.68767123287671228</v>
+        <v>0.71780821917808224</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.25">
@@ -10053,7 +10066,7 @@
       </c>
       <c r="M43">
         <f t="shared" ca="1" si="0"/>
-        <v>8.7917808219178077</v>
+        <v>8.8219178082191778</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
@@ -10093,7 +10106,7 @@
       </c>
       <c r="M44">
         <f t="shared" ca="1" si="0"/>
-        <v>7.1534246575342468</v>
+        <v>7.183561643835616</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.25">
@@ -10135,7 +10148,7 @@
       </c>
       <c r="M45">
         <f t="shared" ca="1" si="0"/>
-        <v>6.6383561643835618</v>
+        <v>6.6684931506849319</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.25">
@@ -10175,7 +10188,7 @@
       </c>
       <c r="M46">
         <f t="shared" ca="1" si="0"/>
-        <v>10.150684931506849</v>
+        <v>10.180821917808219</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
@@ -10215,7 +10228,7 @@
       </c>
       <c r="M47">
         <f t="shared" ca="1" si="0"/>
-        <v>4.1095890410958908</v>
+        <v>4.13972602739726</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.25">
@@ -10255,7 +10268,7 @@
       </c>
       <c r="M48">
         <f t="shared" ca="1" si="0"/>
-        <v>5.7397260273972606</v>
+        <v>5.7698630136986298</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
@@ -10295,7 +10308,7 @@
       </c>
       <c r="M49">
         <f t="shared" ca="1" si="0"/>
-        <v>7.1095890410958908</v>
+        <v>7.13972602739726</v>
       </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.25">
@@ -10335,7 +10348,7 @@
       </c>
       <c r="M50">
         <f t="shared" ca="1" si="0"/>
-        <v>2.978082191780822</v>
+        <v>3.0082191780821916</v>
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.25">
@@ -10377,7 +10390,7 @@
       </c>
       <c r="M51">
         <f t="shared" ca="1" si="0"/>
-        <v>5.7561643835616438</v>
+        <v>5.7863013698630139</v>
       </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.25">
@@ -10419,7 +10432,7 @@
       </c>
       <c r="M52">
         <f t="shared" ca="1" si="0"/>
-        <v>7.3945205479452056</v>
+        <v>7.4246575342465757</v>
       </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.25">
@@ -10459,7 +10472,7 @@
       </c>
       <c r="M53">
         <f t="shared" ca="1" si="0"/>
-        <v>10.304109589041095</v>
+        <v>10.334246575342465</v>
       </c>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.25">
@@ -10499,7 +10512,7 @@
       </c>
       <c r="M54">
         <f t="shared" ca="1" si="0"/>
-        <v>5.0328767123287674</v>
+        <v>5.0630136986301366</v>
       </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.25">
@@ -10541,7 +10554,7 @@
       </c>
       <c r="M55">
         <f t="shared" ca="1" si="0"/>
-        <v>8.6054794520547944</v>
+        <v>8.6356164383561644</v>
       </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.25">
@@ -10583,7 +10596,7 @@
       </c>
       <c r="M56">
         <f t="shared" ca="1" si="0"/>
-        <v>4.3068493150684928</v>
+        <v>4.3369863013698629</v>
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.25">
@@ -10623,7 +10636,7 @@
       </c>
       <c r="M57">
         <f t="shared" ca="1" si="0"/>
-        <v>5.5287671232876709</v>
+        <v>5.558904109589041</v>
       </c>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.25">
@@ -10663,7 +10676,7 @@
       </c>
       <c r="M58">
         <f t="shared" ca="1" si="0"/>
-        <v>7.4986301369863018</v>
+        <v>7.5287671232876709</v>
       </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.25">
@@ -10703,7 +10716,7 @@
       </c>
       <c r="M59">
         <f t="shared" ca="1" si="0"/>
-        <v>9.0273972602739718</v>
+        <v>9.0575342465753419</v>
       </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.25">
@@ -10745,7 +10758,7 @@
       </c>
       <c r="M60">
         <f t="shared" ca="1" si="0"/>
-        <v>6.8657534246575347</v>
+        <v>6.8958904109589039</v>
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.25">
@@ -10785,7 +10798,7 @@
       </c>
       <c r="M61">
         <f t="shared" ca="1" si="0"/>
-        <v>6.3095890410958901</v>
+        <v>6.3397260273972602</v>
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.25">
@@ -10827,7 +10840,7 @@
       </c>
       <c r="M62">
         <f t="shared" ca="1" si="0"/>
-        <v>2.1917808219178081</v>
+        <v>2.2219178082191782</v>
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.25">
@@ -10867,7 +10880,7 @@
       </c>
       <c r="M63">
         <f t="shared" ca="1" si="0"/>
-        <v>3.0739726027397261</v>
+        <v>3.1041095890410957</v>
       </c>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.25">
@@ -10907,7 +10920,7 @@
       </c>
       <c r="M64">
         <f t="shared" ca="1" si="0"/>
-        <v>4.2465753424657535</v>
+        <v>4.2767123287671236</v>
       </c>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.25">
@@ -10947,7 +10960,7 @@
       </c>
       <c r="M65">
         <f t="shared" ca="1" si="0"/>
-        <v>6.3260273972602743</v>
+        <v>6.3561643835616435</v>
       </c>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.25">
@@ -10987,7 +11000,7 @@
       </c>
       <c r="M66">
         <f t="shared" ca="1" si="0"/>
-        <v>1.210958904109589</v>
+        <v>1.2410958904109588</v>
       </c>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.25">
@@ -11027,7 +11040,7 @@
       </c>
       <c r="M67">
         <f t="shared" ref="M67:M130" ca="1" si="1">(TODAY()-H67)/365</f>
-        <v>2.1150684931506851</v>
+        <v>2.1452054794520548</v>
       </c>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.25">
@@ -11067,7 +11080,7 @@
       </c>
       <c r="M68">
         <f t="shared" ca="1" si="1"/>
-        <v>3.0657534246575344</v>
+        <v>3.095890410958904</v>
       </c>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.25">
@@ -11109,7 +11122,7 @@
       </c>
       <c r="M69">
         <f t="shared" ca="1" si="1"/>
-        <v>3.7808219178082192</v>
+        <v>3.8109589041095893</v>
       </c>
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.25">
@@ -11149,7 +11162,7 @@
       </c>
       <c r="M70">
         <f t="shared" ca="1" si="1"/>
-        <v>6.1287671232876715</v>
+        <v>6.1589041095890407</v>
       </c>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.25">
@@ -11189,7 +11202,7 @@
       </c>
       <c r="M71">
         <f t="shared" ca="1" si="1"/>
-        <v>1.7972602739726027</v>
+        <v>1.8273972602739725</v>
       </c>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.25">
@@ -11229,7 +11242,7 @@
       </c>
       <c r="M72">
         <f t="shared" ca="1" si="1"/>
-        <v>1.0465753424657533</v>
+        <v>1.0767123287671232</v>
       </c>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.25">
@@ -11271,7 +11284,7 @@
       </c>
       <c r="M73">
         <f t="shared" ca="1" si="1"/>
-        <v>8.6027397260273979</v>
+        <v>8.632876712328768</v>
       </c>
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.25">
@@ -11311,7 +11324,7 @@
       </c>
       <c r="M74">
         <f t="shared" ca="1" si="1"/>
-        <v>1.021917808219178</v>
+        <v>1.0520547945205478</v>
       </c>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
@@ -11351,7 +11364,7 @@
       </c>
       <c r="M75">
         <f t="shared" ca="1" si="1"/>
-        <v>6.8054794520547945</v>
+        <v>6.8356164383561646</v>
       </c>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.25">
@@ -11393,7 +11406,7 @@
       </c>
       <c r="M76">
         <f t="shared" ca="1" si="1"/>
-        <v>7.441095890410959</v>
+        <v>7.4712328767123291</v>
       </c>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.25">
@@ -11433,7 +11446,7 @@
       </c>
       <c r="M77">
         <f t="shared" ca="1" si="1"/>
-        <v>4.3479452054794523</v>
+        <v>4.3780821917808215</v>
       </c>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.25">
@@ -11473,7 +11486,7 @@
       </c>
       <c r="M78">
         <f t="shared" ca="1" si="1"/>
-        <v>6.0410958904109586</v>
+        <v>6.0712328767123287</v>
       </c>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.25">
@@ -11515,7 +11528,7 @@
       </c>
       <c r="M79">
         <f t="shared" ca="1" si="1"/>
-        <v>2.2082191780821918</v>
+        <v>2.2383561643835614</v>
       </c>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.25">
@@ -11555,7 +11568,7 @@
       </c>
       <c r="M80">
         <f t="shared" ca="1" si="1"/>
-        <v>7.0383561643835613</v>
+        <v>7.0684931506849313</v>
       </c>
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.25">
@@ -11597,7 +11610,7 @@
       </c>
       <c r="M81">
         <f t="shared" ca="1" si="1"/>
-        <v>2.4493150684931506</v>
+        <v>2.4794520547945207</v>
       </c>
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.25">
@@ -11637,7 +11650,7 @@
       </c>
       <c r="M82">
         <f t="shared" ca="1" si="1"/>
-        <v>8.5671232876712331</v>
+        <v>8.5972602739726032</v>
       </c>
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.25">
@@ -11677,7 +11690,7 @@
       </c>
       <c r="M83">
         <f t="shared" ca="1" si="1"/>
-        <v>2.7534246575342465</v>
+        <v>2.7835616438356166</v>
       </c>
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.25">
@@ -11717,7 +11730,7 @@
       </c>
       <c r="M84">
         <f t="shared" ca="1" si="1"/>
-        <v>5.2082191780821914</v>
+        <v>5.2383561643835614</v>
       </c>
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.25">
@@ -11757,7 +11770,7 @@
       </c>
       <c r="M85">
         <f t="shared" ca="1" si="1"/>
-        <v>5.0602739726027401</v>
+        <v>5.0904109589041093</v>
       </c>
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.25">
@@ -11797,7 +11810,7 @@
       </c>
       <c r="M86">
         <f t="shared" ca="1" si="1"/>
-        <v>7.7945205479452051</v>
+        <v>7.8246575342465752</v>
       </c>
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.25">
@@ -11839,7 +11852,7 @@
       </c>
       <c r="M87">
         <f t="shared" ca="1" si="1"/>
-        <v>7.2438356164383562</v>
+        <v>7.2739726027397262</v>
       </c>
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.25">
@@ -11879,7 +11892,7 @@
       </c>
       <c r="M88">
         <f t="shared" ca="1" si="1"/>
-        <v>7.6109589041095891</v>
+        <v>7.6410958904109592</v>
       </c>
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.25">
@@ -11919,7 +11932,7 @@
       </c>
       <c r="M89">
         <f t="shared" ca="1" si="1"/>
-        <v>5.3068493150684928</v>
+        <v>5.3369863013698629</v>
       </c>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.25">
@@ -11961,7 +11974,7 @@
       </c>
       <c r="M90">
         <f t="shared" ca="1" si="1"/>
-        <v>7.6109589041095891</v>
+        <v>7.6410958904109592</v>
       </c>
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.25">
@@ -12001,7 +12014,7 @@
       </c>
       <c r="M91">
         <f t="shared" ca="1" si="1"/>
-        <v>9.9095890410958898</v>
+        <v>9.9397260273972599</v>
       </c>
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.25">
@@ -12041,7 +12054,7 @@
       </c>
       <c r="M92">
         <f t="shared" ca="1" si="1"/>
-        <v>2.7260273972602738</v>
+        <v>2.7561643835616438</v>
       </c>
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.25">
@@ -12081,7 +12094,7 @@
       </c>
       <c r="M93">
         <f t="shared" ca="1" si="1"/>
-        <v>2.3369863013698629</v>
+        <v>2.3671232876712329</v>
       </c>
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.25">
@@ -12121,7 +12134,7 @@
       </c>
       <c r="M94">
         <f t="shared" ca="1" si="1"/>
-        <v>4.1123287671232873</v>
+        <v>4.1424657534246574</v>
       </c>
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.25">
@@ -12161,7 +12174,7 @@
       </c>
       <c r="M95">
         <f t="shared" ca="1" si="1"/>
-        <v>3.4547945205479453</v>
+        <v>3.484931506849315</v>
       </c>
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.25">
@@ -12201,7 +12214,7 @@
       </c>
       <c r="M96">
         <f t="shared" ca="1" si="1"/>
-        <v>6.8794520547945206</v>
+        <v>6.9095890410958907</v>
       </c>
     </row>
     <row r="97" spans="1:13" x14ac:dyDescent="0.25">
@@ -12241,7 +12254,7 @@
       </c>
       <c r="M97">
         <f t="shared" ca="1" si="1"/>
-        <v>7.0493150684931507</v>
+        <v>7.0794520547945208</v>
       </c>
     </row>
     <row r="98" spans="1:13" x14ac:dyDescent="0.25">
@@ -12281,7 +12294,7 @@
       </c>
       <c r="M98">
         <f t="shared" ca="1" si="1"/>
-        <v>5.3945205479452056</v>
+        <v>5.4246575342465757</v>
       </c>
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.25">
@@ -12321,7 +12334,7 @@
       </c>
       <c r="M99">
         <f t="shared" ca="1" si="1"/>
-        <v>8.2958904109589042</v>
+        <v>8.3260273972602743</v>
       </c>
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.25">
@@ -12361,7 +12374,7 @@
       </c>
       <c r="M100">
         <f t="shared" ca="1" si="1"/>
-        <v>1.6109589041095891</v>
+        <v>1.6410958904109589</v>
       </c>
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.25">
@@ -12401,7 +12414,7 @@
       </c>
       <c r="M101">
         <f t="shared" ca="1" si="1"/>
-        <v>5.4</v>
+        <v>5.4301369863013695</v>
       </c>
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.25">
@@ -12441,7 +12454,7 @@
       </c>
       <c r="M102">
         <f t="shared" ca="1" si="1"/>
-        <v>5.9178082191780819</v>
+        <v>5.9479452054794519</v>
       </c>
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.25">
@@ -12481,7 +12494,7 @@
       </c>
       <c r="M103">
         <f t="shared" ca="1" si="1"/>
-        <v>0.88219178082191785</v>
+        <v>0.9123287671232877</v>
       </c>
     </row>
     <row r="104" spans="1:13" x14ac:dyDescent="0.25">
@@ -12521,7 +12534,7 @@
       </c>
       <c r="M104">
         <f t="shared" ca="1" si="1"/>
-        <v>2.4328767123287673</v>
+        <v>2.463013698630137</v>
       </c>
     </row>
     <row r="105" spans="1:13" x14ac:dyDescent="0.25">
@@ -12561,7 +12574,7 @@
       </c>
       <c r="M105">
         <f t="shared" ca="1" si="1"/>
-        <v>6.7068493150684931</v>
+        <v>6.7369863013698632</v>
       </c>
     </row>
     <row r="106" spans="1:13" x14ac:dyDescent="0.25">
@@ -12601,7 +12614,7 @@
       </c>
       <c r="M106">
         <f t="shared" ca="1" si="1"/>
-        <v>4.161643835616438</v>
+        <v>4.1917808219178081</v>
       </c>
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.25">
@@ -12641,7 +12654,7 @@
       </c>
       <c r="M107">
         <f t="shared" ca="1" si="1"/>
-        <v>6.2465753424657535</v>
+        <v>6.2767123287671236</v>
       </c>
     </row>
     <row r="108" spans="1:13" x14ac:dyDescent="0.25">
@@ -12683,7 +12696,7 @@
       </c>
       <c r="M108">
         <f t="shared" ca="1" si="1"/>
-        <v>9.4602739726027405</v>
+        <v>9.4904109589041088</v>
       </c>
     </row>
     <row r="109" spans="1:13" x14ac:dyDescent="0.25">
@@ -12725,7 +12738,7 @@
       </c>
       <c r="M109">
         <f t="shared" ca="1" si="1"/>
-        <v>6.7808219178082192</v>
+        <v>6.8109589041095893</v>
       </c>
     </row>
     <row r="110" spans="1:13" x14ac:dyDescent="0.25">
@@ -12767,7 +12780,7 @@
       </c>
       <c r="M110">
         <f t="shared" ca="1" si="1"/>
-        <v>0.78904109589041094</v>
+        <v>0.81917808219178079</v>
       </c>
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.25">
@@ -12807,7 +12820,7 @@
       </c>
       <c r="M111">
         <f t="shared" ca="1" si="1"/>
-        <v>5.6</v>
+        <v>5.6301369863013697</v>
       </c>
     </row>
     <row r="112" spans="1:13" x14ac:dyDescent="0.25">
@@ -12847,7 +12860,7 @@
       </c>
       <c r="M112">
         <f t="shared" ca="1" si="1"/>
-        <v>5.7452054794520544</v>
+        <v>5.7753424657534245</v>
       </c>
     </row>
     <row r="113" spans="1:13" x14ac:dyDescent="0.25">
@@ -12887,7 +12900,7 @@
       </c>
       <c r="M113">
         <f t="shared" ca="1" si="1"/>
-        <v>3.6246575342465754</v>
+        <v>3.6547945205479451</v>
       </c>
     </row>
     <row r="114" spans="1:13" x14ac:dyDescent="0.25">
@@ -12927,7 +12940,7 @@
       </c>
       <c r="M114">
         <f t="shared" ca="1" si="1"/>
-        <v>7.7150684931506852</v>
+        <v>7.7452054794520544</v>
       </c>
     </row>
     <row r="115" spans="1:13" x14ac:dyDescent="0.25">
@@ -12967,7 +12980,7 @@
       </c>
       <c r="M115">
         <f t="shared" ca="1" si="1"/>
-        <v>3.408219178082192</v>
+        <v>3.4383561643835616</v>
       </c>
     </row>
     <row r="116" spans="1:13" x14ac:dyDescent="0.25">
@@ -13007,7 +13020,7 @@
       </c>
       <c r="M116">
         <f t="shared" ca="1" si="1"/>
-        <v>7.9178082191780819</v>
+        <v>7.9479452054794519</v>
       </c>
     </row>
     <row r="117" spans="1:13" x14ac:dyDescent="0.25">
@@ -13047,7 +13060,7 @@
       </c>
       <c r="M117">
         <f t="shared" ca="1" si="1"/>
-        <v>7.4986301369863018</v>
+        <v>7.5287671232876709</v>
       </c>
     </row>
     <row r="118" spans="1:13" x14ac:dyDescent="0.25">
@@ -13087,7 +13100,7 @@
       </c>
       <c r="M118">
         <f t="shared" ca="1" si="1"/>
-        <v>1.8739726027397261</v>
+        <v>1.904109589041096</v>
       </c>
     </row>
     <row r="119" spans="1:13" x14ac:dyDescent="0.25">
@@ -13127,7 +13140,7 @@
       </c>
       <c r="M119">
         <f t="shared" ca="1" si="1"/>
-        <v>3.5287671232876714</v>
+        <v>3.558904109589041</v>
       </c>
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.25">
@@ -13167,7 +13180,7 @@
       </c>
       <c r="M120">
         <f t="shared" ca="1" si="1"/>
-        <v>2.3616438356164382</v>
+        <v>2.3917808219178083</v>
       </c>
     </row>
     <row r="121" spans="1:13" x14ac:dyDescent="0.25">
@@ -13209,7 +13222,7 @@
       </c>
       <c r="M121">
         <f t="shared" ca="1" si="1"/>
-        <v>1.7534246575342465</v>
+        <v>1.7835616438356163</v>
       </c>
     </row>
     <row r="122" spans="1:13" x14ac:dyDescent="0.25">
@@ -13249,7 +13262,7 @@
       </c>
       <c r="M122">
         <f t="shared" ca="1" si="1"/>
-        <v>2.2027397260273971</v>
+        <v>2.2328767123287672</v>
       </c>
     </row>
     <row r="123" spans="1:13" x14ac:dyDescent="0.25">
@@ -13289,7 +13302,7 @@
       </c>
       <c r="M123">
         <f t="shared" ca="1" si="1"/>
-        <v>6.4739726027397264</v>
+        <v>6.5041095890410956</v>
       </c>
     </row>
     <row r="124" spans="1:13" x14ac:dyDescent="0.25">
@@ -13329,7 +13342,7 @@
       </c>
       <c r="M124">
         <f t="shared" ca="1" si="1"/>
-        <v>6.3041095890410963</v>
+        <v>6.3342465753424655</v>
       </c>
     </row>
     <row r="125" spans="1:13" x14ac:dyDescent="0.25">
@@ -13369,7 +13382,7 @@
       </c>
       <c r="M125">
         <f t="shared" ca="1" si="1"/>
-        <v>3.3123287671232875</v>
+        <v>3.3424657534246576</v>
       </c>
     </row>
     <row r="126" spans="1:13" x14ac:dyDescent="0.25">
@@ -13409,7 +13422,7 @@
       </c>
       <c r="M126">
         <f t="shared" ca="1" si="1"/>
-        <v>10.161643835616438</v>
+        <v>10.191780821917808</v>
       </c>
     </row>
     <row r="127" spans="1:13" x14ac:dyDescent="0.25">
@@ -13451,7 +13464,7 @@
       </c>
       <c r="M127">
         <f t="shared" ca="1" si="1"/>
-        <v>6.4164383561643836</v>
+        <v>6.4465753424657537</v>
       </c>
     </row>
     <row r="128" spans="1:13" x14ac:dyDescent="0.25">
@@ -13491,7 +13504,7 @@
       </c>
       <c r="M128">
         <f t="shared" ca="1" si="1"/>
-        <v>3.6712328767123288</v>
+        <v>3.7013698630136984</v>
       </c>
     </row>
     <row r="129" spans="1:13" x14ac:dyDescent="0.25">
@@ -13531,7 +13544,7 @@
       </c>
       <c r="M129">
         <f t="shared" ca="1" si="1"/>
-        <v>9.4657534246575334</v>
+        <v>9.4958904109589035</v>
       </c>
     </row>
     <row r="130" spans="1:13" x14ac:dyDescent="0.25">
@@ -13571,7 +13584,7 @@
       </c>
       <c r="M130">
         <f t="shared" ca="1" si="1"/>
-        <v>1.0630136986301371</v>
+        <v>1.0931506849315069</v>
       </c>
     </row>
     <row r="131" spans="1:13" x14ac:dyDescent="0.25">
@@ -13611,7 +13624,7 @@
       </c>
       <c r="M131">
         <f t="shared" ref="M131:M194" ca="1" si="2">(TODAY()-H131)/365</f>
-        <v>8.2767123287671236</v>
+        <v>8.3068493150684937</v>
       </c>
     </row>
     <row r="132" spans="1:13" x14ac:dyDescent="0.25">
@@ -13651,7 +13664,7 @@
       </c>
       <c r="M132">
         <f t="shared" ca="1" si="2"/>
-        <v>10.547945205479452</v>
+        <v>10.578082191780823</v>
       </c>
     </row>
     <row r="133" spans="1:13" x14ac:dyDescent="0.25">
@@ -13691,7 +13704,7 @@
       </c>
       <c r="M133">
         <f t="shared" ca="1" si="2"/>
-        <v>9.1013698630136979</v>
+        <v>9.131506849315068</v>
       </c>
     </row>
     <row r="134" spans="1:13" x14ac:dyDescent="0.25">
@@ -13731,7 +13744,7 @@
       </c>
       <c r="M134">
         <f t="shared" ca="1" si="2"/>
-        <v>9.9917808219178088</v>
+        <v>10.021917808219179</v>
       </c>
     </row>
     <row r="135" spans="1:13" x14ac:dyDescent="0.25">
@@ -13771,7 +13784,7 @@
       </c>
       <c r="M135">
         <f t="shared" ca="1" si="2"/>
-        <v>3.9178082191780823</v>
+        <v>3.9479452054794519</v>
       </c>
     </row>
     <row r="136" spans="1:13" x14ac:dyDescent="0.25">
@@ -13811,7 +13824,7 @@
       </c>
       <c r="M136">
         <f t="shared" ca="1" si="2"/>
-        <v>9.8958904109589039</v>
+        <v>9.9260273972602739</v>
       </c>
     </row>
     <row r="137" spans="1:13" x14ac:dyDescent="0.25">
@@ -13851,7 +13864,7 @@
       </c>
       <c r="M137">
         <f t="shared" ca="1" si="2"/>
-        <v>3.7534246575342465</v>
+        <v>3.7835616438356166</v>
       </c>
     </row>
     <row r="138" spans="1:13" x14ac:dyDescent="0.25">
@@ -13893,7 +13906,7 @@
       </c>
       <c r="M138">
         <f t="shared" ca="1" si="2"/>
-        <v>4.9068493150684933</v>
+        <v>4.9369863013698634</v>
       </c>
     </row>
     <row r="139" spans="1:13" x14ac:dyDescent="0.25">
@@ -13933,7 +13946,7 @@
       </c>
       <c r="M139">
         <f t="shared" ca="1" si="2"/>
-        <v>5.5123287671232877</v>
+        <v>5.5424657534246577</v>
       </c>
     </row>
     <row r="140" spans="1:13" x14ac:dyDescent="0.25">
@@ -13973,7 +13986,7 @@
       </c>
       <c r="M140">
         <f t="shared" ca="1" si="2"/>
-        <v>5.7890410958904113</v>
+        <v>5.8191780821917805</v>
       </c>
     </row>
     <row r="141" spans="1:13" x14ac:dyDescent="0.25">
@@ -14013,7 +14026,7 @@
       </c>
       <c r="M141">
         <f t="shared" ca="1" si="2"/>
-        <v>9.5342465753424666</v>
+        <v>9.5643835616438349</v>
       </c>
     </row>
     <row r="142" spans="1:13" x14ac:dyDescent="0.25">
@@ -14055,7 +14068,7 @@
       </c>
       <c r="M142">
         <f t="shared" ca="1" si="2"/>
-        <v>4.2767123287671236</v>
+        <v>4.3068493150684928</v>
       </c>
     </row>
     <row r="143" spans="1:13" x14ac:dyDescent="0.25">
@@ -14095,7 +14108,7 @@
       </c>
       <c r="M143">
         <f t="shared" ca="1" si="2"/>
-        <v>3.8410958904109589</v>
+        <v>3.871232876712329</v>
       </c>
     </row>
     <row r="144" spans="1:13" x14ac:dyDescent="0.25">
@@ -14137,7 +14150,7 @@
       </c>
       <c r="M144">
         <f t="shared" ca="1" si="2"/>
-        <v>1.0931506849315069</v>
+        <v>1.1232876712328768</v>
       </c>
     </row>
     <row r="145" spans="1:13" x14ac:dyDescent="0.25">
@@ -14177,7 +14190,7 @@
       </c>
       <c r="M145">
         <f t="shared" ca="1" si="2"/>
-        <v>3.1972602739726028</v>
+        <v>3.2273972602739724</v>
       </c>
     </row>
     <row r="146" spans="1:13" x14ac:dyDescent="0.25">
@@ -14217,7 +14230,7 @@
       </c>
       <c r="M146">
         <f t="shared" ca="1" si="2"/>
-        <v>0.81917808219178079</v>
+        <v>0.84931506849315064</v>
       </c>
     </row>
     <row r="147" spans="1:13" x14ac:dyDescent="0.25">
@@ -14257,7 +14270,7 @@
       </c>
       <c r="M147">
         <f t="shared" ca="1" si="2"/>
-        <v>8.1643835616438363</v>
+        <v>8.1945205479452063</v>
       </c>
     </row>
     <row r="148" spans="1:13" x14ac:dyDescent="0.25">
@@ -14297,7 +14310,7 @@
       </c>
       <c r="M148">
         <f t="shared" ca="1" si="2"/>
-        <v>3.8876712328767122</v>
+        <v>3.9178082191780823</v>
       </c>
     </row>
     <row r="149" spans="1:13" x14ac:dyDescent="0.25">
@@ -14339,7 +14352,7 @@
       </c>
       <c r="M149">
         <f t="shared" ca="1" si="2"/>
-        <v>5.1287671232876715</v>
+        <v>5.1589041095890407</v>
       </c>
     </row>
     <row r="150" spans="1:13" x14ac:dyDescent="0.25">
@@ -14381,7 +14394,7 @@
       </c>
       <c r="M150">
         <f t="shared" ca="1" si="2"/>
-        <v>5.117808219178082</v>
+        <v>5.1479452054794521</v>
       </c>
     </row>
     <row r="151" spans="1:13" x14ac:dyDescent="0.25">
@@ -14421,7 +14434,7 @@
       </c>
       <c r="M151">
         <f t="shared" ca="1" si="2"/>
-        <v>8.2082191780821923</v>
+        <v>8.2383561643835623</v>
       </c>
     </row>
     <row r="152" spans="1:13" x14ac:dyDescent="0.25">
@@ -14461,7 +14474,7 @@
       </c>
       <c r="M152">
         <f t="shared" ca="1" si="2"/>
-        <v>9.1287671232876715</v>
+        <v>9.1589041095890416</v>
       </c>
     </row>
     <row r="153" spans="1:13" x14ac:dyDescent="0.25">
@@ -14501,7 +14514,7 @@
       </c>
       <c r="M153">
         <f t="shared" ca="1" si="2"/>
-        <v>10.36986301369863</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="154" spans="1:13" x14ac:dyDescent="0.25">
@@ -14541,7 +14554,7 @@
       </c>
       <c r="M154">
         <f t="shared" ca="1" si="2"/>
-        <v>9.287671232876713</v>
+        <v>9.3178082191780813</v>
       </c>
     </row>
     <row r="155" spans="1:13" x14ac:dyDescent="0.25">
@@ -14581,7 +14594,7 @@
       </c>
       <c r="M155">
         <f t="shared" ca="1" si="2"/>
-        <v>9.5917808219178085</v>
+        <v>9.6219178082191785</v>
       </c>
     </row>
     <row r="156" spans="1:13" x14ac:dyDescent="0.25">
@@ -14621,7 +14634,7 @@
       </c>
       <c r="M156">
         <f t="shared" ca="1" si="2"/>
-        <v>8.0931506849315067</v>
+        <v>8.1232876712328768</v>
       </c>
     </row>
     <row r="157" spans="1:13" x14ac:dyDescent="0.25">
@@ -14661,7 +14674,7 @@
       </c>
       <c r="M157">
         <f t="shared" ca="1" si="2"/>
-        <v>2.4164383561643836</v>
+        <v>2.4465753424657533</v>
       </c>
     </row>
     <row r="158" spans="1:13" x14ac:dyDescent="0.25">
@@ -14701,7 +14714,7 @@
       </c>
       <c r="M158">
         <f t="shared" ca="1" si="2"/>
-        <v>8.5917808219178085</v>
+        <v>8.6219178082191785</v>
       </c>
     </row>
     <row r="159" spans="1:13" x14ac:dyDescent="0.25">
@@ -14741,7 +14754,7 @@
       </c>
       <c r="M159">
         <f t="shared" ca="1" si="2"/>
-        <v>8.8849315068493144</v>
+        <v>8.9150684931506845</v>
       </c>
     </row>
     <row r="160" spans="1:13" x14ac:dyDescent="0.25">
@@ -14781,7 +14794,7 @@
       </c>
       <c r="M160">
         <f t="shared" ca="1" si="2"/>
-        <v>4.8849315068493153</v>
+        <v>4.9150684931506845</v>
       </c>
     </row>
     <row r="161" spans="1:13" x14ac:dyDescent="0.25">
@@ -14821,7 +14834,7 @@
       </c>
       <c r="M161">
         <f t="shared" ca="1" si="2"/>
-        <v>3.3452054794520549</v>
+        <v>3.3753424657534246</v>
       </c>
     </row>
     <row r="162" spans="1:13" x14ac:dyDescent="0.25">
@@ -14863,7 +14876,7 @@
       </c>
       <c r="M162">
         <f t="shared" ca="1" si="2"/>
-        <v>5.5315068493150683</v>
+        <v>5.5616438356164384</v>
       </c>
     </row>
     <row r="163" spans="1:13" x14ac:dyDescent="0.25">
@@ -14903,7 +14916,7 @@
       </c>
       <c r="M163">
         <f t="shared" ca="1" si="2"/>
-        <v>1.4794520547945205</v>
+        <v>1.5095890410958903</v>
       </c>
     </row>
     <row r="164" spans="1:13" x14ac:dyDescent="0.25">
@@ -14945,7 +14958,7 @@
       </c>
       <c r="M164">
         <f t="shared" ca="1" si="2"/>
-        <v>4.6986301369863011</v>
+        <v>4.7287671232876711</v>
       </c>
     </row>
     <row r="165" spans="1:13" x14ac:dyDescent="0.25">
@@ -14985,7 +14998,7 @@
       </c>
       <c r="M165">
         <f t="shared" ca="1" si="2"/>
-        <v>9.9917808219178088</v>
+        <v>10.021917808219179</v>
       </c>
     </row>
     <row r="166" spans="1:13" x14ac:dyDescent="0.25">
@@ -15027,7 +15040,7 @@
       </c>
       <c r="M166">
         <f t="shared" ca="1" si="2"/>
-        <v>9.6657534246575345</v>
+        <v>9.6958904109589046</v>
       </c>
     </row>
     <row r="167" spans="1:13" x14ac:dyDescent="0.25">
@@ -15069,7 +15082,7 @@
       </c>
       <c r="M167">
         <f t="shared" ca="1" si="2"/>
-        <v>7.1041095890410961</v>
+        <v>7.1342465753424653</v>
       </c>
     </row>
     <row r="168" spans="1:13" x14ac:dyDescent="0.25">
@@ -15109,7 +15122,7 @@
       </c>
       <c r="M168">
         <f t="shared" ca="1" si="2"/>
-        <v>4.8739726027397259</v>
+        <v>4.904109589041096</v>
       </c>
     </row>
     <row r="169" spans="1:13" x14ac:dyDescent="0.25">
@@ -15149,7 +15162,7 @@
       </c>
       <c r="M169">
         <f t="shared" ca="1" si="2"/>
-        <v>8.0383561643835613</v>
+        <v>8.0684931506849313</v>
       </c>
     </row>
     <row r="170" spans="1:13" x14ac:dyDescent="0.25">
@@ -15191,7 +15204,7 @@
       </c>
       <c r="M170">
         <f t="shared" ca="1" si="2"/>
-        <v>0.74520547945205484</v>
+        <v>0.77534246575342469</v>
       </c>
     </row>
     <row r="171" spans="1:13" x14ac:dyDescent="0.25">
@@ -15231,7 +15244,7 @@
       </c>
       <c r="M171">
         <f t="shared" ca="1" si="2"/>
-        <v>10.09041095890411</v>
+        <v>10.12054794520548</v>
       </c>
     </row>
     <row r="172" spans="1:13" x14ac:dyDescent="0.25">
@@ -15273,7 +15286,7 @@
       </c>
       <c r="M172">
         <f t="shared" ca="1" si="2"/>
-        <v>7.9534246575342467</v>
+        <v>7.9835616438356167</v>
       </c>
     </row>
     <row r="173" spans="1:13" x14ac:dyDescent="0.25">
@@ -15313,7 +15326,7 @@
       </c>
       <c r="M173">
         <f t="shared" ca="1" si="2"/>
-        <v>5.6356164383561644</v>
+        <v>5.6657534246575345</v>
       </c>
     </row>
     <row r="174" spans="1:13" x14ac:dyDescent="0.25">
@@ -15353,7 +15366,7 @@
       </c>
       <c r="M174">
         <f t="shared" ca="1" si="2"/>
-        <v>9.9945205479452053</v>
+        <v>10.024657534246575</v>
       </c>
     </row>
     <row r="175" spans="1:13" x14ac:dyDescent="0.25">
@@ -15393,7 +15406,7 @@
       </c>
       <c r="M175">
         <f t="shared" ca="1" si="2"/>
-        <v>9.6383561643835609</v>
+        <v>9.668493150684931</v>
       </c>
     </row>
     <row r="176" spans="1:13" x14ac:dyDescent="0.25">
@@ -15433,7 +15446,7 @@
       </c>
       <c r="M176">
         <f t="shared" ca="1" si="2"/>
-        <v>0.65205479452054793</v>
+        <v>0.68219178082191778</v>
       </c>
     </row>
     <row r="177" spans="1:13" x14ac:dyDescent="0.25">
@@ -15473,7 +15486,7 @@
       </c>
       <c r="M177">
         <f t="shared" ca="1" si="2"/>
-        <v>6.3726027397260276</v>
+        <v>6.4027397260273968</v>
       </c>
     </row>
     <row r="178" spans="1:13" x14ac:dyDescent="0.25">
@@ -15513,7 +15526,7 @@
       </c>
       <c r="M178">
         <f t="shared" ca="1" si="2"/>
-        <v>10.150684931506849</v>
+        <v>10.180821917808219</v>
       </c>
     </row>
     <row r="179" spans="1:13" x14ac:dyDescent="0.25">
@@ -15553,7 +15566,7 @@
       </c>
       <c r="M179">
         <f t="shared" ca="1" si="2"/>
-        <v>9.6904109589041099</v>
+        <v>9.7205479452054799</v>
       </c>
     </row>
     <row r="180" spans="1:13" x14ac:dyDescent="0.25">
@@ -15593,7 +15606,7 @@
       </c>
       <c r="M180">
         <f t="shared" ca="1" si="2"/>
-        <v>1.8684931506849316</v>
+        <v>1.8986301369863015</v>
       </c>
     </row>
     <row r="181" spans="1:13" x14ac:dyDescent="0.25">
@@ -15633,7 +15646,7 @@
       </c>
       <c r="M181">
         <f t="shared" ca="1" si="2"/>
-        <v>9.3342465753424655</v>
+        <v>9.3643835616438356</v>
       </c>
     </row>
     <row r="182" spans="1:13" x14ac:dyDescent="0.25">
@@ -15673,7 +15686,7 @@
       </c>
       <c r="M182">
         <f t="shared" ca="1" si="2"/>
-        <v>3.6794520547945204</v>
+        <v>3.7095890410958905</v>
       </c>
     </row>
     <row r="183" spans="1:13" x14ac:dyDescent="0.25">
@@ -15715,7 +15728,7 @@
       </c>
       <c r="M183">
         <f t="shared" ca="1" si="2"/>
-        <v>4.6767123287671231</v>
+        <v>4.7068493150684931</v>
       </c>
     </row>
     <row r="184" spans="1:13" x14ac:dyDescent="0.25">
@@ -15755,7 +15768,7 @@
       </c>
       <c r="M184">
         <f t="shared" ca="1" si="2"/>
-        <v>6.3890410958904109</v>
+        <v>6.419178082191781</v>
       </c>
     </row>
     <row r="185" spans="1:13" x14ac:dyDescent="0.25">
@@ -15795,7 +15808,7 @@
       </c>
       <c r="M185">
         <f t="shared" ca="1" si="2"/>
-        <v>2.3287671232876712</v>
+        <v>2.3589041095890413</v>
       </c>
     </row>
     <row r="186" spans="1:13" x14ac:dyDescent="0.25">
@@ -15835,7 +15848,7 @@
       </c>
       <c r="M186">
         <f t="shared" ca="1" si="2"/>
-        <v>3.4904109589041097</v>
+        <v>3.5205479452054793</v>
       </c>
     </row>
     <row r="187" spans="1:13" x14ac:dyDescent="0.25">
@@ -15875,7 +15888,7 @@
       </c>
       <c r="M187">
         <f t="shared" ca="1" si="2"/>
-        <v>0.63835616438356169</v>
+        <v>0.66849315068493154</v>
       </c>
     </row>
     <row r="188" spans="1:13" x14ac:dyDescent="0.25">
@@ -15915,7 +15928,7 @@
       </c>
       <c r="M188">
         <f t="shared" ca="1" si="2"/>
-        <v>2.1260273972602741</v>
+        <v>2.1561643835616437</v>
       </c>
     </row>
     <row r="189" spans="1:13" x14ac:dyDescent="0.25">
@@ -15955,7 +15968,7 @@
       </c>
       <c r="M189">
         <f t="shared" ca="1" si="2"/>
-        <v>5.6767123287671231</v>
+        <v>5.7068493150684931</v>
       </c>
     </row>
     <row r="190" spans="1:13" x14ac:dyDescent="0.25">
@@ -15997,7 +16010,7 @@
       </c>
       <c r="M190">
         <f t="shared" ca="1" si="2"/>
-        <v>6.4575342465753423</v>
+        <v>6.4876712328767123</v>
       </c>
     </row>
     <row r="191" spans="1:13" x14ac:dyDescent="0.25">
@@ -16037,7 +16050,7 @@
       </c>
       <c r="M191">
         <f t="shared" ca="1" si="2"/>
-        <v>7.2821917808219174</v>
+        <v>7.3123287671232875</v>
       </c>
     </row>
     <row r="192" spans="1:13" x14ac:dyDescent="0.25">
@@ -16077,7 +16090,7 @@
       </c>
       <c r="M192">
         <f t="shared" ca="1" si="2"/>
-        <v>8.7095890410958905</v>
+        <v>8.7397260273972606</v>
       </c>
     </row>
     <row r="193" spans="1:13" x14ac:dyDescent="0.25">
@@ -16117,7 +16130,7 @@
       </c>
       <c r="M193">
         <f t="shared" ca="1" si="2"/>
-        <v>9.7369863013698623</v>
+        <v>9.7671232876712324</v>
       </c>
     </row>
     <row r="194" spans="1:13" x14ac:dyDescent="0.25">
@@ -16157,7 +16170,7 @@
       </c>
       <c r="M194">
         <f t="shared" ca="1" si="2"/>
-        <v>9.161643835616438</v>
+        <v>9.1917808219178081</v>
       </c>
     </row>
     <row r="195" spans="1:13" x14ac:dyDescent="0.25">
@@ -16197,7 +16210,7 @@
       </c>
       <c r="M195">
         <f t="shared" ref="M195:M201" ca="1" si="3">(TODAY()-H195)/365</f>
-        <v>8.8575342465753426</v>
+        <v>8.8876712328767127</v>
       </c>
     </row>
     <row r="196" spans="1:13" x14ac:dyDescent="0.25">
@@ -16237,7 +16250,7 @@
       </c>
       <c r="M196">
         <f t="shared" ca="1" si="3"/>
-        <v>7.0520547945205481</v>
+        <v>7.0821917808219181</v>
       </c>
     </row>
     <row r="197" spans="1:13" x14ac:dyDescent="0.25">
@@ -16277,7 +16290,7 @@
       </c>
       <c r="M197">
         <f t="shared" ca="1" si="3"/>
-        <v>4.2767123287671236</v>
+        <v>4.3068493150684928</v>
       </c>
     </row>
     <row r="198" spans="1:13" x14ac:dyDescent="0.25">
@@ -16317,7 +16330,7 @@
       </c>
       <c r="M198">
         <f t="shared" ca="1" si="3"/>
-        <v>8.3342465753424655</v>
+        <v>8.3643835616438356</v>
       </c>
     </row>
     <row r="199" spans="1:13" x14ac:dyDescent="0.25">
@@ -16357,7 +16370,7 @@
       </c>
       <c r="M199">
         <f t="shared" ca="1" si="3"/>
-        <v>3.0849315068493151</v>
+        <v>3.1150684931506851</v>
       </c>
     </row>
     <row r="200" spans="1:13" x14ac:dyDescent="0.25">
@@ -16397,7 +16410,7 @@
       </c>
       <c r="M200">
         <f t="shared" ca="1" si="3"/>
-        <v>1.6739726027397259</v>
+        <v>1.704109589041096</v>
       </c>
     </row>
     <row r="201" spans="1:13" x14ac:dyDescent="0.25">
@@ -16439,7 +16452,7 @@
       </c>
       <c r="M201">
         <f t="shared" ca="1" si="3"/>
-        <v>6.5287671232876709</v>
+        <v>6.558904109589041</v>
       </c>
     </row>
   </sheetData>
@@ -16464,10 +16477,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="25.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="6" t="s">
         <v>527</v>
       </c>
-      <c r="B1" s="6">
+      <c r="B1" s="10">
         <f>COUNTIFS(Table1[EmploymentStatus],"Active")</f>
         <v>156</v>
       </c>
@@ -16479,7 +16492,7 @@
       </c>
     </row>
     <row r="2" spans="1:5" ht="25.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="6" t="s">
         <v>528</v>
       </c>
       <c r="B2" s="8">
@@ -16502,28 +16515,28 @@
       </c>
     </row>
     <row r="4" spans="1:5" ht="25.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="6" t="s">
         <v>532</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="9">
         <f ca="1">AVERAGEIFS(Table1[TenureYears],Table1[EmploymentStatus],"Active")</f>
-        <v>5.7536354056901997</v>
+        <v>5.7837723919915742</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="25.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="6" t="s">
         <v>533</v>
       </c>
-      <c r="B6" s="9">
+      <c r="B6" s="11">
         <f>COUNTIFS(Table1[Gender],"Female",Table1[EmploymentStatus],"Active")/$B$1</f>
         <v>0.50641025641025639</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="25.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="7" t="s">
         <v>534</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B7" s="11">
         <f>COUNTIFS(Table1[Gender],"Male",Table1[EmploymentStatus],"Active")/$B$1</f>
         <v>0.49358974358974361</v>
       </c>

--- a/hr_employee_data.xlsx
+++ b/hr_employee_data.xlsx
@@ -5,7 +5,7 @@
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\The Moor\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\The Moor\Desktop\Project\hr-kpi-excel-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1668" uniqueCount="537">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1674" uniqueCount="537">
   <si>
     <t>EmployeeID</t>
   </si>
@@ -1631,9 +1631,6 @@
     <t>Grand Total</t>
   </si>
   <si>
-    <t>Sum of AnnualSalary</t>
-  </si>
-  <si>
     <t>Average Tenure (Years)</t>
   </si>
   <si>
@@ -1647,6 +1644,9 @@
   </si>
   <si>
     <t>Count</t>
+  </si>
+  <si>
+    <t>Average of AnnualSalary</t>
   </si>
 </sst>
 </file>
@@ -2065,6 +2065,36 @@
   </c:pivotSource>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Average Salary</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> by Department</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
@@ -2205,10 +2235,28 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Dashboard!$D$2:$D$3</c:f>
+              <c:f>Dashboard!$D$2:$D$9</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
+                  <c:v>Customer Support</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Engineering</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Finance</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Human Resources</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Marketing</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Operations</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>Sales</c:v>
                 </c:pt>
               </c:strCache>
@@ -2216,12 +2264,30 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Dashboard!$E$2:$E$3</c:f>
+              <c:f>Dashboard!$E$2:$E$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>1901625</c:v>
+                  <c:v>44325.413793103449</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>72146.370370370365</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>63969.120000000003</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>54989.08</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>55320.909090909088</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>64724.1</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>59425.78125</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2237,11 +2303,11 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="345475008"/>
-        <c:axId val="345475392"/>
+        <c:axId val="159596544"/>
+        <c:axId val="342282856"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="345475008"/>
+        <c:axId val="159596544"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2284,7 +2350,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="345475392"/>
+        <c:crossAx val="342282856"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2292,7 +2358,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="345475392"/>
+        <c:axId val="342282856"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2343,7 +2409,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="345475008"/>
+        <c:crossAx val="159596544"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2450,6 +2516,31 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Gender split</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
@@ -2651,6 +2742,35 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Performance</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> Rating Distribution</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
@@ -2689,67 +2809,10 @@
         <c:grouping val="clustered"/>
         <c:varyColors val="0"/>
         <c:ser>
-          <c:idx val="0"/>
+          <c:idx val="1"/>
           <c:order val="0"/>
           <c:tx>
-            <c:strRef>
-              <c:f>Dashboard!$A$9</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Rating</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:val>
-            <c:numRef>
-              <c:f>Dashboard!$A$10:$A$14</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Dashboard!$B$9</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Count</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:v>Count</c:v>
           </c:tx>
           <c:spPr>
             <a:solidFill>
@@ -2761,29 +2824,47 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numLit>
+              <c:formatCode>General</c:formatCode>
+              <c:ptCount val="5"/>
+              <c:pt idx="0">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>2</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>3</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>4</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>5</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:cat>
           <c:val>
-            <c:numRef>
-              <c:f>Dashboard!$B$10:$B$14</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>22</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>77</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>63</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>32</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
+            <c:numLit>
+              <c:formatCode>General</c:formatCode>
+              <c:ptCount val="5"/>
+              <c:pt idx="0">
+                <c:v>6</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>22</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>77</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>63</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>32</c:v>
+              </c:pt>
+            </c:numLit>
           </c:val>
         </c:ser>
         <c:dLbls>
@@ -2796,16 +2877,17 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="346758712"/>
-        <c:axId val="346764752"/>
+        <c:axId val="342348224"/>
+        <c:axId val="342603752"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="346758712"/>
+        <c:axId val="342348224"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -2842,7 +2924,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="346764752"/>
+        <c:crossAx val="342603752"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2850,7 +2932,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="346764752"/>
+        <c:axId val="342603752"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2901,7 +2983,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="346758712"/>
+        <c:crossAx val="342348224"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2913,38 +2995,6 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="b"/>
-      <c:layout/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
@@ -4638,7 +4688,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>581025</xdr:colOff>
+      <xdr:colOff>1986643</xdr:colOff>
       <xdr:row>29</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:to>
@@ -4662,15 +4712,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>235743</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>95251</xdr:rowOff>
+      <xdr:colOff>480671</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>108858</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>590550</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>171451</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>223157</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>185058</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -4722,18 +4772,18 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>642937</xdr:colOff>
+      <xdr:colOff>1990043</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>145256</xdr:rowOff>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>1138237</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>221454</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>2381</xdr:rowOff>
+      <xdr:rowOff>68037</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="5" name="Department"/>
@@ -4750,7 +4800,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -4760,8 +4810,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="4643437" y="3657600"/>
-              <a:ext cx="1828800" cy="2524125"/>
+              <a:off x="6645387" y="3512345"/>
+              <a:ext cx="1827098" cy="2735036"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -7884,7 +7934,7 @@
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
-  <location ref="D1:E3" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <location ref="D1:E9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="13">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -7915,12 +7965,12 @@
     </pivotField>
     <pivotField axis="axisRow" showAll="0" sortType="ascending">
       <items count="8">
-        <item h="1" x="3"/>
-        <item h="1" x="5"/>
-        <item h="1" x="2"/>
-        <item h="1" x="4"/>
-        <item h="1" x="0"/>
-        <item h="1" x="6"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item x="0"/>
+        <item x="6"/>
         <item x="1"/>
         <item t="default"/>
       </items>
@@ -7938,7 +7988,25 @@
   <rowFields count="1">
     <field x="3"/>
   </rowFields>
-  <rowItems count="2">
+  <rowItems count="8">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
     <i>
       <x v="6"/>
     </i>
@@ -7950,7 +8018,7 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Sum of AnnualSalary" fld="10" baseField="0" baseItem="0"/>
+    <dataField name="Average of AnnualSalary" fld="10" subtotal="average" baseField="3" baseItem="0"/>
   </dataFields>
   <chartFormats count="1">
     <chartFormat chart="0" format="2" series="1">
@@ -7980,12 +8048,12 @@
   <data>
     <tabular pivotCacheId="1">
       <items count="7">
-        <i x="3"/>
-        <i x="5"/>
-        <i x="2"/>
-        <i x="4"/>
-        <i x="0"/>
-        <i x="6"/>
+        <i x="3" s="1"/>
+        <i x="5" s="1"/>
+        <i x="2" s="1"/>
+        <i x="4" s="1"/>
+        <i x="0" s="1"/>
+        <i x="6" s="1"/>
         <i x="1" s="1"/>
       </items>
     </tabular>
@@ -16468,12 +16536,17 @@
   <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.140625" customWidth="1"/>
     <col min="2" max="2" width="12.42578125" customWidth="1"/>
-    <col min="4" max="4" width="14.140625" customWidth="1"/>
-    <col min="5" max="5" width="20" customWidth="1"/>
-    <col min="6" max="6" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" customWidth="1"/>
+    <col min="5" max="5" width="31.140625" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="7" max="7" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.28515625" customWidth="1"/>
+    <col min="9" max="9" width="13" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="25.5" x14ac:dyDescent="0.35">
@@ -16488,7 +16561,7 @@
         <v>529</v>
       </c>
       <c r="E1" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="25.5" x14ac:dyDescent="0.35">
@@ -16500,53 +16573,93 @@
         <v>0.22</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="E2" s="5">
-        <v>1901625</v>
+        <v>44325.413793103449</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D3" s="4" t="s">
-        <v>530</v>
+        <v>62</v>
       </c>
       <c r="E3" s="5">
-        <v>1901625</v>
+        <v>72146.370370370365</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="25.5" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B4" s="9">
         <f ca="1">AVERAGEIFS(Table1[TenureYears],Table1[EmploymentStatus],"Active")</f>
         <v>5.7837723919915742</v>
       </c>
+      <c r="D4" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" s="5">
+        <v>63969.120000000003</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D5" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E5" s="5">
+        <v>54989.08</v>
+      </c>
     </row>
     <row r="6" spans="1:5" ht="25.5" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B6" s="11">
         <f>COUNTIFS(Table1[Gender],"Female",Table1[EmploymentStatus],"Active")/$B$1</f>
         <v>0.50641025641025639</v>
       </c>
+      <c r="D6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="5">
+        <v>55320.909090909088</v>
+      </c>
     </row>
     <row r="7" spans="1:5" ht="25.5" x14ac:dyDescent="0.35">
       <c r="A7" s="7" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B7" s="11">
         <f>COUNTIFS(Table1[Gender],"Male",Table1[EmploymentStatus],"Active")/$B$1</f>
         <v>0.49358974358974361</v>
       </c>
+      <c r="D7" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E7" s="5">
+        <v>64724.1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D8" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="5">
+        <v>59425.78125</v>
+      </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>534</v>
+      </c>
+      <c r="B9" t="s">
         <v>535</v>
       </c>
-      <c r="B9" t="s">
-        <v>536</v>
+      <c r="D9" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="E9" s="5">
+        <v>59574.964999999997</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
